--- a/data/original/Larvae.xlsx
+++ b/data/original/Larvae.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://irtacat-my.sharepoint.com/personal/alejandro_munoz_irta_cat/Documents/Documentos/Exclusion-Lisso-Analysis/data/original/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{F98A0A30-A346-49C5-A2F3-5DF01623BBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FC9025B-017C-41C1-8693-5981F9C22E4C}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{F98A0A30-A346-49C5-A2F3-5DF01623BBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18DD6E05-3D65-4F96-8A55-08A31B2D290C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-7515" windowWidth="29040" windowHeight="15720" xr2:uid="{46C13484-1FF9-4DFC-AA32-BC60FC8665E5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="17">
   <si>
     <t>FE</t>
   </si>
@@ -79,13 +79,22 @@
   <si>
     <t>Repeat</t>
   </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Core</t>
+  </si>
+  <si>
+    <t>Whole plant</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -125,30 +134,19 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -243,6 +241,35 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -262,14 +289,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AEE8C3E0-BFFC-4C4F-A6EF-BEAECF2FDB75}" name="Tabla1" displayName="Tabla1" ref="A1:F501" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A1:F501" xr:uid="{DEE25006-57C4-468D-9204-AB3F3B6C19D3}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E5400A99-6876-4766-8AD1-FADB1C5595A3}" name="Date" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AEE8C3E0-BFFC-4C4F-A6EF-BEAECF2FDB75}" name="Tabla1" displayName="Tabla1" ref="A1:G501" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G501" xr:uid="{DEE25006-57C4-468D-9204-AB3F3B6C19D3}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E5400A99-6876-4766-8AD1-FADB1C5595A3}" name="Date" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{909CE776-F84E-4BE5-A6C4-F97962D04069}" name="Field" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{B27F255F-A962-43BA-8F77-7CAA9303B848}" name="Treatment" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{0A2420D5-37B8-48B6-AC97-BE0BD3B95F70}" name="Repeat" dataDxfId="3"/>
     <tableColumn id="5" xr3:uid="{0299E61D-981B-4C11-B285-EC3D621BD3B0}" name="Abundance" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{828AD81F-46C2-46F2-8E84-685E00848C4B}" name="Method" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{02EC2731-B94A-418B-AE20-B517AAD4F3B3}" name="Observations" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -277,9 +305,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -317,7 +345,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -423,7 +451,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -565,7 +593,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -573,18 +601,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFEBE04C-2E8B-4704-AA34-3A285004F75D}">
-  <dimension ref="A1:F501"/>
+  <dimension ref="A1:G501"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="2" width="8.54296875" customWidth="1"/>
     <col min="3" max="3" width="12.26953125" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.6328125" customWidth="1"/>
-    <col min="6" max="6" width="63.08984375" customWidth="1"/>
+    <col min="5" max="6" width="12.6328125" customWidth="1"/>
+    <col min="7" max="7" width="63.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -601,10 +629,13 @@
         <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>45819</v>
       </c>
@@ -620,9 +651,12 @@
       <c r="E2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>45819</v>
       </c>
@@ -638,9 +672,12 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>45819</v>
       </c>
@@ -656,9 +693,12 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>45819</v>
       </c>
@@ -674,9 +714,12 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>45819</v>
       </c>
@@ -692,9 +735,12 @@
       <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>45819</v>
       </c>
@@ -710,9 +756,12 @@
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>45819</v>
       </c>
@@ -728,9 +777,12 @@
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>45819</v>
       </c>
@@ -746,9 +798,12 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>45819</v>
       </c>
@@ -764,9 +819,12 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>45819</v>
       </c>
@@ -782,9 +840,12 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>45819</v>
       </c>
@@ -800,9 +861,12 @@
       <c r="E12" s="1">
         <v>0</v>
       </c>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>45819</v>
       </c>
@@ -818,9 +882,12 @@
       <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>45819</v>
       </c>
@@ -836,9 +903,12 @@
       <c r="E14" s="1">
         <v>0</v>
       </c>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>45819</v>
       </c>
@@ -854,9 +924,12 @@
       <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>45819</v>
       </c>
@@ -872,9 +945,12 @@
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>45819</v>
       </c>
@@ -890,9 +966,12 @@
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>45819</v>
       </c>
@@ -908,9 +987,12 @@
       <c r="E18" s="1">
         <v>0</v>
       </c>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>45819</v>
       </c>
@@ -926,9 +1008,12 @@
       <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>45819</v>
       </c>
@@ -944,9 +1029,12 @@
       <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>45819</v>
       </c>
@@ -962,9 +1050,12 @@
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>45819</v>
       </c>
@@ -980,9 +1071,12 @@
       <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>45819</v>
       </c>
@@ -998,9 +1092,12 @@
       <c r="E23" s="1">
         <v>0</v>
       </c>
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>45819</v>
       </c>
@@ -1016,9 +1113,12 @@
       <c r="E24" s="1">
         <v>0</v>
       </c>
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>45819</v>
       </c>
@@ -1034,9 +1134,12 @@
       <c r="E25" s="1">
         <v>0</v>
       </c>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>45819</v>
       </c>
@@ -1052,9 +1155,12 @@
       <c r="E26" s="1">
         <v>0</v>
       </c>
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>45819</v>
       </c>
@@ -1070,9 +1176,12 @@
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>45819</v>
       </c>
@@ -1088,9 +1197,12 @@
       <c r="E28" s="1">
         <v>3</v>
       </c>
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>45819</v>
       </c>
@@ -1106,9 +1218,12 @@
       <c r="E29" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>45819</v>
       </c>
@@ -1124,9 +1239,12 @@
       <c r="E30" s="1">
         <v>0</v>
       </c>
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>45819</v>
       </c>
@@ -1142,9 +1260,12 @@
       <c r="E31" s="1">
         <v>5</v>
       </c>
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>45819</v>
       </c>
@@ -1160,9 +1281,12 @@
       <c r="E32" s="1">
         <v>0</v>
       </c>
-      <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>45819</v>
       </c>
@@ -1178,9 +1302,12 @@
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>45819</v>
       </c>
@@ -1196,9 +1323,12 @@
       <c r="E34" s="1">
         <v>0</v>
       </c>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>45819</v>
       </c>
@@ -1214,9 +1344,12 @@
       <c r="E35" s="1">
         <v>0</v>
       </c>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>45819</v>
       </c>
@@ -1232,9 +1365,12 @@
       <c r="E36" s="1">
         <v>0</v>
       </c>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>45819</v>
       </c>
@@ -1250,9 +1386,12 @@
       <c r="E37" s="1">
         <v>1</v>
       </c>
-      <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>45819</v>
       </c>
@@ -1268,9 +1407,12 @@
       <c r="E38" s="1">
         <v>1</v>
       </c>
-      <c r="F38" s="1"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>45819</v>
       </c>
@@ -1286,9 +1428,12 @@
       <c r="E39" s="1">
         <v>0</v>
       </c>
-      <c r="F39" s="1"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>45819</v>
       </c>
@@ -1304,9 +1449,12 @@
       <c r="E40" s="1">
         <v>0</v>
       </c>
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>45819</v>
       </c>
@@ -1322,9 +1470,12 @@
       <c r="E41" s="1">
         <v>0</v>
       </c>
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>45819</v>
       </c>
@@ -1340,9 +1491,12 @@
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="1"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>45819</v>
       </c>
@@ -1358,9 +1512,12 @@
       <c r="E43" s="1">
         <v>0</v>
       </c>
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>45819</v>
       </c>
@@ -1376,9 +1533,12 @@
       <c r="E44" s="1">
         <v>0</v>
       </c>
-      <c r="F44" s="1"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>45819</v>
       </c>
@@ -1394,9 +1554,12 @@
       <c r="E45" s="1">
         <v>1</v>
       </c>
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45819</v>
       </c>
@@ -1412,9 +1575,12 @@
       <c r="E46" s="1">
         <v>0</v>
       </c>
-      <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45819</v>
       </c>
@@ -1430,9 +1596,12 @@
       <c r="E47" s="1">
         <v>1</v>
       </c>
-      <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>45819</v>
       </c>
@@ -1448,9 +1617,12 @@
       <c r="E48" s="1">
         <v>0</v>
       </c>
-      <c r="F48" s="1"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>45819</v>
       </c>
@@ -1466,9 +1638,12 @@
       <c r="E49" s="1">
         <v>1</v>
       </c>
-      <c r="F49" s="1"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>45819</v>
       </c>
@@ -1484,9 +1659,12 @@
       <c r="E50" s="1">
         <v>1</v>
       </c>
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>45819</v>
       </c>
@@ -1502,9 +1680,12 @@
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="1"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>45819</v>
       </c>
@@ -1520,9 +1701,12 @@
       <c r="E52" s="1">
         <v>0</v>
       </c>
-      <c r="F52" s="1"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>45819</v>
       </c>
@@ -1538,9 +1722,12 @@
       <c r="E53" s="1">
         <v>0</v>
       </c>
-      <c r="F53" s="1"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>45819</v>
       </c>
@@ -1556,9 +1743,12 @@
       <c r="E54" s="1">
         <v>0</v>
       </c>
-      <c r="F54" s="1"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>45819</v>
       </c>
@@ -1574,9 +1764,12 @@
       <c r="E55" s="1">
         <v>0</v>
       </c>
-      <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>45819</v>
       </c>
@@ -1592,9 +1785,12 @@
       <c r="E56" s="1">
         <v>0</v>
       </c>
-      <c r="F56" s="1"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>45819</v>
       </c>
@@ -1610,9 +1806,12 @@
       <c r="E57" s="1">
         <v>0</v>
       </c>
-      <c r="F57" s="1"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>45819</v>
       </c>
@@ -1628,9 +1827,12 @@
       <c r="E58" s="1">
         <v>5</v>
       </c>
-      <c r="F58" s="1"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>45819</v>
       </c>
@@ -1646,9 +1848,12 @@
       <c r="E59" s="1">
         <v>1</v>
       </c>
-      <c r="F59" s="1"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>45819</v>
       </c>
@@ -1664,9 +1869,12 @@
       <c r="E60" s="1">
         <v>0</v>
       </c>
-      <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>45819</v>
       </c>
@@ -1682,9 +1890,12 @@
       <c r="E61" s="1">
         <v>0</v>
       </c>
-      <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>45820</v>
       </c>
@@ -1700,9 +1911,12 @@
       <c r="E62" s="1">
         <v>0</v>
       </c>
-      <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" s="1"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>45820</v>
       </c>
@@ -1718,9 +1932,12 @@
       <c r="E63" s="1">
         <v>0</v>
       </c>
-      <c r="F63" s="1"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" s="1"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>45820</v>
       </c>
@@ -1736,9 +1953,12 @@
       <c r="E64" s="1">
         <v>0</v>
       </c>
-      <c r="F64" s="1"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>45820</v>
       </c>
@@ -1754,9 +1974,12 @@
       <c r="E65" s="1">
         <v>1</v>
       </c>
-      <c r="F65" s="1"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" s="1"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>45820</v>
       </c>
@@ -1772,9 +1995,12 @@
       <c r="E66" s="1">
         <v>0</v>
       </c>
-      <c r="F66" s="1"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>45820</v>
       </c>
@@ -1790,9 +2016,12 @@
       <c r="E67" s="1">
         <v>4</v>
       </c>
-      <c r="F67" s="1"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" s="1"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>45820</v>
       </c>
@@ -1808,9 +2037,12 @@
       <c r="E68" s="1">
         <v>0</v>
       </c>
-      <c r="F68" s="1"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" s="1"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>45820</v>
       </c>
@@ -1826,9 +2058,12 @@
       <c r="E69" s="1">
         <v>3</v>
       </c>
-      <c r="F69" s="1"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" s="1"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>45820</v>
       </c>
@@ -1844,9 +2079,12 @@
       <c r="E70" s="1">
         <v>0</v>
       </c>
-      <c r="F70" s="1"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" s="1"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>45820</v>
       </c>
@@ -1862,9 +2100,12 @@
       <c r="E71" s="1">
         <v>0</v>
       </c>
-      <c r="F71" s="1"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" s="1"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>45820</v>
       </c>
@@ -1880,9 +2121,12 @@
       <c r="E72" s="1">
         <v>0</v>
       </c>
-      <c r="F72" s="1"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="1"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>45820</v>
       </c>
@@ -1898,9 +2142,12 @@
       <c r="E73" s="1">
         <v>0</v>
       </c>
-      <c r="F73" s="1"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" s="1"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>45820</v>
       </c>
@@ -1916,9 +2163,12 @@
       <c r="E74" s="1">
         <v>0</v>
       </c>
-      <c r="F74" s="1"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" s="1"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>45820</v>
       </c>
@@ -1934,9 +2184,12 @@
       <c r="E75" s="1">
         <v>0</v>
       </c>
-      <c r="F75" s="1"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" s="1"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>45820</v>
       </c>
@@ -1952,9 +2205,12 @@
       <c r="E76" s="1">
         <v>0</v>
       </c>
-      <c r="F76" s="1"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" s="1"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>45820</v>
       </c>
@@ -1970,9 +2226,12 @@
       <c r="E77" s="1">
         <v>0</v>
       </c>
-      <c r="F77" s="1"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" s="1"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>45820</v>
       </c>
@@ -1988,9 +2247,12 @@
       <c r="E78" s="1">
         <v>1</v>
       </c>
-      <c r="F78" s="1"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" s="1"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>45820</v>
       </c>
@@ -2006,9 +2268,12 @@
       <c r="E79" s="1">
         <v>0</v>
       </c>
-      <c r="F79" s="1"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="1"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>45820</v>
       </c>
@@ -2024,9 +2289,12 @@
       <c r="E80" s="1">
         <v>1</v>
       </c>
-      <c r="F80" s="1"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G80" s="1"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>45820</v>
       </c>
@@ -2042,9 +2310,12 @@
       <c r="E81" s="1">
         <v>0</v>
       </c>
-      <c r="F81" s="1"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" s="1"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>45819</v>
       </c>
@@ -2060,9 +2331,12 @@
       <c r="E82" s="1">
         <v>0</v>
       </c>
-      <c r="F82" s="1"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="1"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>45819</v>
       </c>
@@ -2078,9 +2352,12 @@
       <c r="E83" s="1">
         <v>0</v>
       </c>
-      <c r="F83" s="1"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" s="1"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>45819</v>
       </c>
@@ -2096,9 +2373,12 @@
       <c r="E84" s="1">
         <v>0</v>
       </c>
-      <c r="F84" s="1"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="1"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>45819</v>
       </c>
@@ -2114,9 +2394,12 @@
       <c r="E85" s="1">
         <v>0</v>
       </c>
-      <c r="F85" s="1"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F85" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="1"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>45819</v>
       </c>
@@ -2132,9 +2415,12 @@
       <c r="E86" s="1">
         <v>0</v>
       </c>
-      <c r="F86" s="1"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86" s="1"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>45819</v>
       </c>
@@ -2150,9 +2436,12 @@
       <c r="E87" s="1">
         <v>0</v>
       </c>
-      <c r="F87" s="1"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G87" s="1"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>45819</v>
       </c>
@@ -2168,9 +2457,12 @@
       <c r="E88" s="1">
         <v>0</v>
       </c>
-      <c r="F88" s="1"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F88" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" s="1"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>45819</v>
       </c>
@@ -2186,9 +2478,12 @@
       <c r="E89" s="1">
         <v>0</v>
       </c>
-      <c r="F89" s="1"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" s="1"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>45819</v>
       </c>
@@ -2204,9 +2499,12 @@
       <c r="E90" s="1">
         <v>0</v>
       </c>
-      <c r="F90" s="1"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F90" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G90" s="1"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>45819</v>
       </c>
@@ -2222,9 +2520,12 @@
       <c r="E91" s="1">
         <v>0</v>
       </c>
-      <c r="F91" s="1"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F91" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G91" s="1"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>45819</v>
       </c>
@@ -2240,9 +2541,12 @@
       <c r="E92" s="1">
         <v>0</v>
       </c>
-      <c r="F92" s="1"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" s="1"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>45819</v>
       </c>
@@ -2258,9 +2562,12 @@
       <c r="E93" s="1">
         <v>0</v>
       </c>
-      <c r="F93" s="1"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F93" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" s="1"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>45819</v>
       </c>
@@ -2276,9 +2583,12 @@
       <c r="E94" s="1">
         <v>0</v>
       </c>
-      <c r="F94" s="1"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94" s="1"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>45819</v>
       </c>
@@ -2294,9 +2604,12 @@
       <c r="E95" s="1">
         <v>0</v>
       </c>
-      <c r="F95" s="1"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F95" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G95" s="1"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>45819</v>
       </c>
@@ -2312,9 +2625,12 @@
       <c r="E96" s="1">
         <v>0</v>
       </c>
-      <c r="F96" s="1"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96" s="1"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>45819</v>
       </c>
@@ -2330,9 +2646,12 @@
       <c r="E97" s="1">
         <v>0</v>
       </c>
-      <c r="F97" s="1"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F97" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97" s="1"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>45819</v>
       </c>
@@ -2348,9 +2667,12 @@
       <c r="E98" s="1">
         <v>0</v>
       </c>
-      <c r="F98" s="1"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F98" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G98" s="1"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>45819</v>
       </c>
@@ -2366,9 +2688,12 @@
       <c r="E99" s="1">
         <v>0</v>
       </c>
-      <c r="F99" s="1"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F99" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G99" s="1"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>45819</v>
       </c>
@@ -2384,9 +2709,12 @@
       <c r="E100" s="1">
         <v>0</v>
       </c>
-      <c r="F100" s="1"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F100" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G100" s="1"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>45819</v>
       </c>
@@ -2402,9 +2730,12 @@
       <c r="E101" s="1">
         <v>0</v>
       </c>
-      <c r="F101" s="1"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G101" s="1"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>45827</v>
       </c>
@@ -2421,10 +2752,13 @@
         <v>7</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>45827</v>
       </c>
@@ -2440,9 +2774,12 @@
       <c r="E103" s="1">
         <v>1</v>
       </c>
-      <c r="F103" s="1"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F103" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" s="1"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>45827</v>
       </c>
@@ -2458,9 +2795,12 @@
       <c r="E104" s="1">
         <v>2</v>
       </c>
-      <c r="F104" s="1"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F104" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G104" s="1"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>45827</v>
       </c>
@@ -2476,9 +2816,12 @@
       <c r="E105" s="1">
         <v>1</v>
       </c>
-      <c r="F105" s="1"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F105" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G105" s="1"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>45827</v>
       </c>
@@ -2494,9 +2837,12 @@
       <c r="E106" s="1">
         <v>1</v>
       </c>
-      <c r="F106" s="1"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F106" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>45827</v>
       </c>
@@ -2512,9 +2858,12 @@
       <c r="E107" s="1">
         <v>1</v>
       </c>
-      <c r="F107" s="1"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F107" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G107" s="1"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>45827</v>
       </c>
@@ -2530,9 +2879,12 @@
       <c r="E108" s="1">
         <v>0</v>
       </c>
-      <c r="F108" s="1"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F108" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G108" s="1"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>45827</v>
       </c>
@@ -2548,9 +2900,12 @@
       <c r="E109" s="1">
         <v>3</v>
       </c>
-      <c r="F109" s="1"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F109" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" s="1"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>45827</v>
       </c>
@@ -2566,9 +2921,12 @@
       <c r="E110" s="1">
         <v>1</v>
       </c>
-      <c r="F110" s="1"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F110" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" s="1"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>45827</v>
       </c>
@@ -2584,9 +2942,12 @@
       <c r="E111" s="1">
         <v>3</v>
       </c>
-      <c r="F111" s="1"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F111" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" s="1"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>45827</v>
       </c>
@@ -2602,9 +2963,12 @@
       <c r="E112" s="1">
         <v>0</v>
       </c>
-      <c r="F112" s="1"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F112" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G112" s="1"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>45827</v>
       </c>
@@ -2620,9 +2984,12 @@
       <c r="E113" s="1">
         <v>4</v>
       </c>
-      <c r="F113" s="1"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F113" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" s="1"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>45827</v>
       </c>
@@ -2638,9 +3005,12 @@
       <c r="E114" s="1">
         <v>1</v>
       </c>
-      <c r="F114" s="1"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F114" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" s="1"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>45827</v>
       </c>
@@ -2656,9 +3026,12 @@
       <c r="E115" s="1">
         <v>5</v>
       </c>
-      <c r="F115" s="1"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F115" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G115" s="1"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>45827</v>
       </c>
@@ -2674,9 +3047,12 @@
       <c r="E116" s="1">
         <v>8</v>
       </c>
-      <c r="F116" s="1"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F116" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" s="1"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>45827</v>
       </c>
@@ -2692,9 +3068,12 @@
       <c r="E117" s="1">
         <v>2</v>
       </c>
-      <c r="F117" s="1"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F117" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G117" s="1"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>45827</v>
       </c>
@@ -2710,9 +3089,12 @@
       <c r="E118" s="1">
         <v>3</v>
       </c>
-      <c r="F118" s="1"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F118" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" s="1"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>45827</v>
       </c>
@@ -2728,9 +3110,12 @@
       <c r="E119" s="1">
         <v>0</v>
       </c>
-      <c r="F119" s="1"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F119" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" s="1"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>45827</v>
       </c>
@@ -2746,9 +3131,12 @@
       <c r="E120" s="1">
         <v>0</v>
       </c>
-      <c r="F120" s="1"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G120" s="1"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>45827</v>
       </c>
@@ -2764,9 +3152,12 @@
       <c r="E121" s="1">
         <v>0</v>
       </c>
-      <c r="F121" s="1"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F121" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" s="1"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>45827</v>
       </c>
@@ -2782,9 +3173,12 @@
       <c r="E122" s="1">
         <v>0</v>
       </c>
-      <c r="F122" s="1"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F122" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G122" s="1"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>45827</v>
       </c>
@@ -2800,9 +3194,12 @@
       <c r="E123" s="1">
         <v>2</v>
       </c>
-      <c r="F123" s="1"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F123" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G123" s="1"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>45827</v>
       </c>
@@ -2818,9 +3215,12 @@
       <c r="E124" s="1">
         <v>2</v>
       </c>
-      <c r="F124" s="1"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F124" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" s="1"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>45827</v>
       </c>
@@ -2836,9 +3236,12 @@
       <c r="E125" s="1">
         <v>2</v>
       </c>
-      <c r="F125" s="1"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F125" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" s="1"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>45827</v>
       </c>
@@ -2854,9 +3257,12 @@
       <c r="E126" s="1">
         <v>0</v>
       </c>
-      <c r="F126" s="1"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F126" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" s="1"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>45827</v>
       </c>
@@ -2872,9 +3278,12 @@
       <c r="E127" s="1">
         <v>1</v>
       </c>
-      <c r="F127" s="1"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F127" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G127" s="1"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>45827</v>
       </c>
@@ -2890,9 +3299,12 @@
       <c r="E128" s="1">
         <v>0</v>
       </c>
-      <c r="F128" s="1"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F128" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" s="1"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>45827</v>
       </c>
@@ -2908,9 +3320,12 @@
       <c r="E129" s="1">
         <v>0</v>
       </c>
-      <c r="F129" s="1"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F129" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" s="1"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>45827</v>
       </c>
@@ -2926,9 +3341,12 @@
       <c r="E130" s="1">
         <v>0</v>
       </c>
-      <c r="F130" s="1"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F130" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G130" s="1"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>45827</v>
       </c>
@@ -2944,9 +3362,12 @@
       <c r="E131" s="1">
         <v>3</v>
       </c>
-      <c r="F131" s="1"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F131" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G131" s="1"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>45827</v>
       </c>
@@ -2962,9 +3383,12 @@
       <c r="E132" s="1">
         <v>1</v>
       </c>
-      <c r="F132" s="1"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F132" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G132" s="1"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>45827</v>
       </c>
@@ -2980,9 +3404,12 @@
       <c r="E133" s="1">
         <v>0</v>
       </c>
-      <c r="F133" s="1"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F133" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G133" s="1"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>45827</v>
       </c>
@@ -2998,9 +3425,12 @@
       <c r="E134" s="1">
         <v>1</v>
       </c>
-      <c r="F134" s="1"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F134" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G134" s="1"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>45827</v>
       </c>
@@ -3016,9 +3446,12 @@
       <c r="E135" s="1">
         <v>0</v>
       </c>
-      <c r="F135" s="1"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F135" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G135" s="1"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>45827</v>
       </c>
@@ -3034,9 +3467,12 @@
       <c r="E136" s="1">
         <v>3</v>
       </c>
-      <c r="F136" s="1"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F136" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G136" s="1"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>45827</v>
       </c>
@@ -3052,9 +3488,12 @@
       <c r="E137" s="1">
         <v>0</v>
       </c>
-      <c r="F137" s="1"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F137" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G137" s="1"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>45827</v>
       </c>
@@ -3070,9 +3509,12 @@
       <c r="E138" s="1">
         <v>4</v>
       </c>
-      <c r="F138" s="1"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F138" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G138" s="1"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>45827</v>
       </c>
@@ -3088,9 +3530,12 @@
       <c r="E139" s="1">
         <v>0</v>
       </c>
-      <c r="F139" s="1"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F139" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G139" s="1"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>45827</v>
       </c>
@@ -3106,9 +3551,12 @@
       <c r="E140" s="1">
         <v>2</v>
       </c>
-      <c r="F140" s="1"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F140" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G140" s="1"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>45827</v>
       </c>
@@ -3124,9 +3572,12 @@
       <c r="E141" s="1">
         <v>0</v>
       </c>
-      <c r="F141" s="1"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F141" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" s="1"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>45827</v>
       </c>
@@ -3142,9 +3593,12 @@
       <c r="E142" s="1">
         <v>6</v>
       </c>
-      <c r="F142" s="1"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F142" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G142" s="1"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>45827</v>
       </c>
@@ -3160,9 +3614,12 @@
       <c r="E143" s="1">
         <v>3</v>
       </c>
-      <c r="F143" s="1"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F143" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G143" s="1"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>45827</v>
       </c>
@@ -3178,9 +3635,12 @@
       <c r="E144" s="1">
         <v>2</v>
       </c>
-      <c r="F144" s="1"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F144" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G144" s="1"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>45827</v>
       </c>
@@ -3196,9 +3656,12 @@
       <c r="E145" s="1">
         <v>2</v>
       </c>
-      <c r="F145" s="1"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F145" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G145" s="1"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>45827</v>
       </c>
@@ -3214,9 +3677,12 @@
       <c r="E146" s="1">
         <v>0</v>
       </c>
-      <c r="F146" s="1"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F146" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G146" s="1"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>45827</v>
       </c>
@@ -3232,9 +3698,12 @@
       <c r="E147" s="1">
         <v>3</v>
       </c>
-      <c r="F147" s="1"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F147" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G147" s="1"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>45827</v>
       </c>
@@ -3250,9 +3719,12 @@
       <c r="E148" s="1">
         <v>1</v>
       </c>
-      <c r="F148" s="1"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F148" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G148" s="1"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>45827</v>
       </c>
@@ -3268,9 +3740,12 @@
       <c r="E149" s="1">
         <v>4</v>
       </c>
-      <c r="F149" s="1"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F149" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G149" s="1"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>45827</v>
       </c>
@@ -3286,9 +3761,12 @@
       <c r="E150" s="1">
         <v>5</v>
       </c>
-      <c r="F150" s="1"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F150" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G150" s="1"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>45827</v>
       </c>
@@ -3304,9 +3782,12 @@
       <c r="E151" s="1">
         <v>4</v>
       </c>
-      <c r="F151" s="1"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F151" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G151" s="1"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>45827</v>
       </c>
@@ -3322,9 +3803,12 @@
       <c r="E152" s="1">
         <v>3</v>
       </c>
-      <c r="F152" s="1"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F152" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G152" s="1"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>45827</v>
       </c>
@@ -3340,9 +3824,12 @@
       <c r="E153" s="1">
         <v>5</v>
       </c>
-      <c r="F153" s="1"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F153" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G153" s="1"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>45827</v>
       </c>
@@ -3358,9 +3845,12 @@
       <c r="E154" s="1">
         <v>10</v>
       </c>
-      <c r="F154" s="1"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F154" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G154" s="1"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>45827</v>
       </c>
@@ -3376,9 +3866,12 @@
       <c r="E155" s="1">
         <v>1</v>
       </c>
-      <c r="F155" s="1"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F155" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G155" s="1"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>45827</v>
       </c>
@@ -3394,9 +3887,12 @@
       <c r="E156" s="1">
         <v>6</v>
       </c>
-      <c r="F156" s="1"/>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F156" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G156" s="1"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>45827</v>
       </c>
@@ -3412,9 +3908,12 @@
       <c r="E157" s="1">
         <v>2</v>
       </c>
-      <c r="F157" s="1"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F157" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G157" s="1"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>45827</v>
       </c>
@@ -3430,9 +3929,12 @@
       <c r="E158" s="1">
         <v>6</v>
       </c>
-      <c r="F158" s="1"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F158" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G158" s="1"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>45827</v>
       </c>
@@ -3448,9 +3950,12 @@
       <c r="E159" s="1">
         <v>2</v>
       </c>
-      <c r="F159" s="1"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F159" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G159" s="1"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>45827</v>
       </c>
@@ -3466,9 +3971,12 @@
       <c r="E160" s="1">
         <v>8</v>
       </c>
-      <c r="F160" s="1"/>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F160" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G160" s="1"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>45827</v>
       </c>
@@ -3484,9 +3992,12 @@
       <c r="E161" s="1">
         <v>7</v>
       </c>
-      <c r="F161" s="1"/>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F161" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G161" s="1"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>45827</v>
       </c>
@@ -3502,9 +4013,12 @@
       <c r="E162" s="1">
         <v>2</v>
       </c>
-      <c r="F162" s="1"/>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F162" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G162" s="1"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>45827</v>
       </c>
@@ -3520,9 +4034,12 @@
       <c r="E163" s="1">
         <v>5</v>
       </c>
-      <c r="F163" s="1"/>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F163" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G163" s="1"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>45827</v>
       </c>
@@ -3538,9 +4055,12 @@
       <c r="E164" s="1">
         <v>0</v>
       </c>
-      <c r="F164" s="1"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F164" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G164" s="1"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>45827</v>
       </c>
@@ -3556,9 +4076,12 @@
       <c r="E165" s="1">
         <v>1</v>
       </c>
-      <c r="F165" s="1"/>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F165" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G165" s="1"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>45827</v>
       </c>
@@ -3574,9 +4097,12 @@
       <c r="E166" s="1">
         <v>0</v>
       </c>
-      <c r="F166" s="1"/>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F166" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G166" s="1"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>45827</v>
       </c>
@@ -3592,9 +4118,12 @@
       <c r="E167" s="1">
         <v>2</v>
       </c>
-      <c r="F167" s="1"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F167" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G167" s="1"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>45827</v>
       </c>
@@ -3610,9 +4139,12 @@
       <c r="E168" s="1">
         <v>2</v>
       </c>
-      <c r="F168" s="1"/>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F168" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G168" s="1"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>45827</v>
       </c>
@@ -3628,9 +4160,12 @@
       <c r="E169" s="1">
         <v>0</v>
       </c>
-      <c r="F169" s="1"/>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F169" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G169" s="1"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>45827</v>
       </c>
@@ -3646,9 +4181,12 @@
       <c r="E170" s="1">
         <v>0</v>
       </c>
-      <c r="F170" s="1"/>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F170" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G170" s="1"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>45827</v>
       </c>
@@ -3664,9 +4202,12 @@
       <c r="E171" s="1">
         <v>3</v>
       </c>
-      <c r="F171" s="1"/>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F171" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G171" s="1"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>45827</v>
       </c>
@@ -3682,9 +4223,12 @@
       <c r="E172" s="1">
         <v>2</v>
       </c>
-      <c r="F172" s="1"/>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F172" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G172" s="1"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>45827</v>
       </c>
@@ -3700,9 +4244,12 @@
       <c r="E173" s="1">
         <v>10</v>
       </c>
-      <c r="F173" s="1"/>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F173" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G173" s="1"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>45827</v>
       </c>
@@ -3718,9 +4265,12 @@
       <c r="E174" s="1">
         <v>4</v>
       </c>
-      <c r="F174" s="1"/>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F174" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G174" s="1"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>45827</v>
       </c>
@@ -3736,9 +4286,12 @@
       <c r="E175" s="1">
         <v>1</v>
       </c>
-      <c r="F175" s="1"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F175" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G175" s="1"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>45827</v>
       </c>
@@ -3754,9 +4307,12 @@
       <c r="E176" s="1">
         <v>1</v>
       </c>
-      <c r="F176" s="1"/>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F176" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G176" s="1"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>45827</v>
       </c>
@@ -3772,9 +4328,12 @@
       <c r="E177" s="1">
         <v>0</v>
       </c>
-      <c r="F177" s="1"/>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F177" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G177" s="1"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>45827</v>
       </c>
@@ -3790,9 +4349,12 @@
       <c r="E178" s="1">
         <v>1</v>
       </c>
-      <c r="F178" s="1"/>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F178" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G178" s="1"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>45827</v>
       </c>
@@ -3808,9 +4370,12 @@
       <c r="E179" s="1">
         <v>1</v>
       </c>
-      <c r="F179" s="1"/>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F179" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G179" s="1"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>45827</v>
       </c>
@@ -3826,9 +4391,12 @@
       <c r="E180" s="1">
         <v>4</v>
       </c>
-      <c r="F180" s="1"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F180" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G180" s="1"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>45827</v>
       </c>
@@ -3844,9 +4412,12 @@
       <c r="E181" s="1">
         <v>2</v>
       </c>
-      <c r="F181" s="1"/>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F181" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G181" s="1"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>45827</v>
       </c>
@@ -3862,9 +4433,12 @@
       <c r="E182" s="1">
         <v>1</v>
       </c>
-      <c r="F182" s="1"/>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F182" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G182" s="1"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>45827</v>
       </c>
@@ -3880,9 +4454,12 @@
       <c r="E183" s="1">
         <v>2</v>
       </c>
-      <c r="F183" s="1"/>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F183" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G183" s="1"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>45827</v>
       </c>
@@ -3898,9 +4475,12 @@
       <c r="E184" s="1">
         <v>5</v>
       </c>
-      <c r="F184" s="1"/>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F184" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G184" s="1"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>45827</v>
       </c>
@@ -3916,9 +4496,12 @@
       <c r="E185" s="1">
         <v>4</v>
       </c>
-      <c r="F185" s="1"/>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F185" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G185" s="1"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>45827</v>
       </c>
@@ -3934,9 +4517,12 @@
       <c r="E186" s="1">
         <v>3</v>
       </c>
-      <c r="F186" s="1"/>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F186" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G186" s="1"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>45827</v>
       </c>
@@ -3952,9 +4538,12 @@
       <c r="E187" s="1">
         <v>3</v>
       </c>
-      <c r="F187" s="1"/>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F187" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G187" s="1"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>45827</v>
       </c>
@@ -3970,9 +4559,12 @@
       <c r="E188" s="1">
         <v>13</v>
       </c>
-      <c r="F188" s="1"/>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F188" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G188" s="1"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>45827</v>
       </c>
@@ -3988,9 +4580,12 @@
       <c r="E189" s="1">
         <v>0</v>
       </c>
-      <c r="F189" s="1"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F189" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G189" s="1"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>45827</v>
       </c>
@@ -4006,9 +4601,12 @@
       <c r="E190" s="1">
         <v>3</v>
       </c>
-      <c r="F190" s="1"/>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F190" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G190" s="1"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>45827</v>
       </c>
@@ -4024,9 +4622,12 @@
       <c r="E191" s="1">
         <v>1</v>
       </c>
-      <c r="F191" s="1"/>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F191" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G191" s="1"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>45827</v>
       </c>
@@ -4042,9 +4643,12 @@
       <c r="E192" s="1">
         <v>0</v>
       </c>
-      <c r="F192" s="1"/>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F192" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G192" s="1"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>45827</v>
       </c>
@@ -4060,9 +4664,12 @@
       <c r="E193" s="1">
         <v>0</v>
       </c>
-      <c r="F193" s="1"/>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F193" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G193" s="1"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>45827</v>
       </c>
@@ -4078,9 +4685,12 @@
       <c r="E194" s="1">
         <v>4</v>
       </c>
-      <c r="F194" s="1"/>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F194" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G194" s="1"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>45827</v>
       </c>
@@ -4096,9 +4706,12 @@
       <c r="E195" s="1">
         <v>0</v>
       </c>
-      <c r="F195" s="1"/>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F195" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G195" s="1"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>45827</v>
       </c>
@@ -4114,9 +4727,12 @@
       <c r="E196" s="1">
         <v>4</v>
       </c>
-      <c r="F196" s="1"/>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F196" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G196" s="1"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>45827</v>
       </c>
@@ -4132,9 +4748,12 @@
       <c r="E197" s="1">
         <v>2</v>
       </c>
-      <c r="F197" s="1"/>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F197" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G197" s="1"/>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>45827</v>
       </c>
@@ -4150,9 +4769,12 @@
       <c r="E198" s="1">
         <v>8</v>
       </c>
-      <c r="F198" s="1"/>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F198" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G198" s="1"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>45827</v>
       </c>
@@ -4168,9 +4790,12 @@
       <c r="E199" s="1">
         <v>1</v>
       </c>
-      <c r="F199" s="1"/>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F199" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G199" s="1"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>45827</v>
       </c>
@@ -4186,9 +4811,12 @@
       <c r="E200" s="1">
         <v>1</v>
       </c>
-      <c r="F200" s="1"/>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F200" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G200" s="1"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>45827</v>
       </c>
@@ -4204,9 +4832,12 @@
       <c r="E201" s="1">
         <v>0</v>
       </c>
-      <c r="F201" s="1"/>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F201" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G201" s="1"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>45838</v>
       </c>
@@ -4223,10 +4854,13 @@
         <v>0</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>45838</v>
       </c>
@@ -4242,9 +4876,12 @@
       <c r="E203" s="1">
         <v>2</v>
       </c>
-      <c r="F203" s="1"/>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F203" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G203" s="1"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>45838</v>
       </c>
@@ -4260,9 +4897,12 @@
       <c r="E204" s="1">
         <v>8</v>
       </c>
-      <c r="F204" s="1"/>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F204" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G204" s="1"/>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>45838</v>
       </c>
@@ -4278,9 +4918,12 @@
       <c r="E205" s="1">
         <v>3</v>
       </c>
-      <c r="F205" s="1"/>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F205" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G205" s="1"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>45838</v>
       </c>
@@ -4296,9 +4939,12 @@
       <c r="E206" s="1">
         <v>1</v>
       </c>
-      <c r="F206" s="1"/>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F206" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G206" s="1"/>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>45838</v>
       </c>
@@ -4314,9 +4960,12 @@
       <c r="E207" s="1">
         <v>1</v>
       </c>
-      <c r="F207" s="1"/>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F207" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G207" s="1"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>45838</v>
       </c>
@@ -4332,9 +4981,12 @@
       <c r="E208" s="1">
         <v>4</v>
       </c>
-      <c r="F208" s="1"/>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F208" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G208" s="1"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>45838</v>
       </c>
@@ -4350,9 +5002,12 @@
       <c r="E209" s="1">
         <v>9</v>
       </c>
-      <c r="F209" s="1"/>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F209" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G209" s="1"/>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>45838</v>
       </c>
@@ -4368,9 +5023,12 @@
       <c r="E210" s="1">
         <v>2</v>
       </c>
-      <c r="F210" s="1"/>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F210" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G210" s="1"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>45838</v>
       </c>
@@ -4387,10 +5045,13 @@
         <v>5</v>
       </c>
       <c r="F211" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G211" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>45838</v>
       </c>
@@ -4406,9 +5067,12 @@
       <c r="E212" s="1">
         <v>2</v>
       </c>
-      <c r="F212" s="1"/>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F212" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G212" s="1"/>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>45838</v>
       </c>
@@ -4424,9 +5088,12 @@
       <c r="E213" s="1">
         <v>3</v>
       </c>
-      <c r="F213" s="1"/>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F213" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G213" s="1"/>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>45838</v>
       </c>
@@ -4442,9 +5109,12 @@
       <c r="E214" s="1">
         <v>0</v>
       </c>
-      <c r="F214" s="1"/>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F214" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G214" s="1"/>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>45838</v>
       </c>
@@ -4460,9 +5130,12 @@
       <c r="E215" s="1">
         <v>1</v>
       </c>
-      <c r="F215" s="1"/>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F215" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G215" s="1"/>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>45838</v>
       </c>
@@ -4478,9 +5151,12 @@
       <c r="E216" s="1">
         <v>3</v>
       </c>
-      <c r="F216" s="1"/>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F216" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G216" s="1"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>45838</v>
       </c>
@@ -4496,9 +5172,12 @@
       <c r="E217" s="1">
         <v>3</v>
       </c>
-      <c r="F217" s="1"/>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F217" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G217" s="1"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>45838</v>
       </c>
@@ -4514,9 +5193,12 @@
       <c r="E218" s="1">
         <v>3</v>
       </c>
-      <c r="F218" s="1"/>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F218" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G218" s="1"/>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>45838</v>
       </c>
@@ -4532,9 +5214,12 @@
       <c r="E219" s="1">
         <v>2</v>
       </c>
-      <c r="F219" s="1"/>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F219" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G219" s="1"/>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>45838</v>
       </c>
@@ -4550,9 +5235,12 @@
       <c r="E220" s="1">
         <v>6</v>
       </c>
-      <c r="F220" s="1"/>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F220" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G220" s="1"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>45838</v>
       </c>
@@ -4568,9 +5256,12 @@
       <c r="E221" s="1">
         <v>1</v>
       </c>
-      <c r="F221" s="1"/>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F221" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G221" s="1"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>45838</v>
       </c>
@@ -4586,9 +5277,12 @@
       <c r="E222" s="1">
         <v>0</v>
       </c>
-      <c r="F222" s="1"/>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F222" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G222" s="1"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>45838</v>
       </c>
@@ -4604,9 +5298,12 @@
       <c r="E223" s="1">
         <v>0</v>
       </c>
-      <c r="F223" s="1"/>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F223" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G223" s="1"/>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>45838</v>
       </c>
@@ -4622,9 +5319,12 @@
       <c r="E224" s="1">
         <v>3</v>
       </c>
-      <c r="F224" s="1"/>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F224" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G224" s="1"/>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>45838</v>
       </c>
@@ -4640,9 +5340,12 @@
       <c r="E225" s="1">
         <v>3</v>
       </c>
-      <c r="F225" s="1"/>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F225" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G225" s="1"/>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>45838</v>
       </c>
@@ -4658,9 +5361,12 @@
       <c r="E226" s="1">
         <v>2</v>
       </c>
-      <c r="F226" s="1"/>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F226" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G226" s="1"/>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>45838</v>
       </c>
@@ -4676,9 +5382,12 @@
       <c r="E227" s="1">
         <v>1</v>
       </c>
-      <c r="F227" s="1"/>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F227" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G227" s="1"/>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>45838</v>
       </c>
@@ -4694,9 +5403,12 @@
       <c r="E228" s="1">
         <v>0</v>
       </c>
-      <c r="F228" s="1"/>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F228" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G228" s="1"/>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>45838</v>
       </c>
@@ -4712,9 +5424,12 @@
       <c r="E229" s="1">
         <v>1</v>
       </c>
-      <c r="F229" s="1"/>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F229" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G229" s="1"/>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>45838</v>
       </c>
@@ -4730,9 +5445,12 @@
       <c r="E230" s="1">
         <v>1</v>
       </c>
-      <c r="F230" s="1"/>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F230" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G230" s="1"/>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>45838</v>
       </c>
@@ -4748,9 +5466,12 @@
       <c r="E231" s="1">
         <v>0</v>
       </c>
-      <c r="F231" s="1"/>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F231" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G231" s="1"/>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>45838</v>
       </c>
@@ -4766,9 +5487,12 @@
       <c r="E232" s="1">
         <v>1</v>
       </c>
-      <c r="F232" s="1"/>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F232" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G232" s="1"/>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>45838</v>
       </c>
@@ -4784,9 +5508,12 @@
       <c r="E233" s="1">
         <v>1</v>
       </c>
-      <c r="F233" s="1"/>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F233" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G233" s="1"/>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>45838</v>
       </c>
@@ -4802,9 +5529,12 @@
       <c r="E234" s="1">
         <v>0</v>
       </c>
-      <c r="F234" s="1"/>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F234" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G234" s="1"/>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>45838</v>
       </c>
@@ -4820,9 +5550,12 @@
       <c r="E235" s="1">
         <v>2</v>
       </c>
-      <c r="F235" s="1"/>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F235" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G235" s="1"/>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>45838</v>
       </c>
@@ -4838,9 +5571,12 @@
       <c r="E236" s="1">
         <v>0</v>
       </c>
-      <c r="F236" s="1"/>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F236" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G236" s="1"/>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>45838</v>
       </c>
@@ -4856,9 +5592,12 @@
       <c r="E237" s="1">
         <v>6</v>
       </c>
-      <c r="F237" s="1"/>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F237" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G237" s="1"/>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>45838</v>
       </c>
@@ -4874,9 +5613,12 @@
       <c r="E238" s="1">
         <v>3</v>
       </c>
-      <c r="F238" s="1"/>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F238" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G238" s="1"/>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>45838</v>
       </c>
@@ -4892,9 +5634,12 @@
       <c r="E239" s="1">
         <v>0</v>
       </c>
-      <c r="F239" s="1"/>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F239" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G239" s="1"/>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>45838</v>
       </c>
@@ -4910,9 +5655,12 @@
       <c r="E240" s="1">
         <v>0</v>
       </c>
-      <c r="F240" s="1"/>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F240" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G240" s="1"/>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>45838</v>
       </c>
@@ -4928,9 +5676,12 @@
       <c r="E241" s="1">
         <v>5</v>
       </c>
-      <c r="F241" s="1"/>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F241" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G241" s="1"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>45838</v>
       </c>
@@ -4946,9 +5697,12 @@
       <c r="E242" s="1">
         <v>2</v>
       </c>
-      <c r="F242" s="1"/>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F242" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G242" s="1"/>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>45838</v>
       </c>
@@ -4964,9 +5718,12 @@
       <c r="E243" s="1">
         <v>3</v>
       </c>
-      <c r="F243" s="1"/>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F243" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G243" s="1"/>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>45838</v>
       </c>
@@ -4982,9 +5739,12 @@
       <c r="E244" s="1">
         <v>10</v>
       </c>
-      <c r="F244" s="1"/>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F244" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G244" s="1"/>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="2">
         <v>45838</v>
       </c>
@@ -5000,9 +5760,12 @@
       <c r="E245" s="1">
         <v>7</v>
       </c>
-      <c r="F245" s="1"/>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F245" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G245" s="1"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="2">
         <v>45838</v>
       </c>
@@ -5018,9 +5781,12 @@
       <c r="E246" s="1">
         <v>5</v>
       </c>
-      <c r="F246" s="1"/>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F246" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G246" s="1"/>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="2">
         <v>45838</v>
       </c>
@@ -5036,9 +5802,12 @@
       <c r="E247" s="1">
         <v>3</v>
       </c>
-      <c r="F247" s="1"/>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F247" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G247" s="1"/>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="2">
         <v>45838</v>
       </c>
@@ -5054,9 +5823,12 @@
       <c r="E248" s="1">
         <v>1</v>
       </c>
-      <c r="F248" s="1"/>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F248" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G248" s="1"/>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="2">
         <v>45838</v>
       </c>
@@ -5072,9 +5844,12 @@
       <c r="E249" s="1">
         <v>10</v>
       </c>
-      <c r="F249" s="1"/>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F249" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G249" s="1"/>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="2">
         <v>45838</v>
       </c>
@@ -5090,9 +5865,12 @@
       <c r="E250" s="1">
         <v>3</v>
       </c>
-      <c r="F250" s="1"/>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F250" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G250" s="1"/>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="2">
         <v>45838</v>
       </c>
@@ -5108,9 +5886,12 @@
       <c r="E251" s="1">
         <v>4</v>
       </c>
-      <c r="F251" s="1"/>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F251" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G251" s="1"/>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="2">
         <v>45838</v>
       </c>
@@ -5126,9 +5907,12 @@
       <c r="E252" s="1">
         <v>5</v>
       </c>
-      <c r="F252" s="1"/>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F252" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G252" s="1"/>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="2">
         <v>45838</v>
       </c>
@@ -5144,9 +5928,12 @@
       <c r="E253" s="1">
         <v>8</v>
       </c>
-      <c r="F253" s="1"/>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F253" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G253" s="1"/>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="2">
         <v>45838</v>
       </c>
@@ -5162,9 +5949,12 @@
       <c r="E254" s="1">
         <v>1</v>
       </c>
-      <c r="F254" s="1"/>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F254" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G254" s="1"/>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="2">
         <v>45838</v>
       </c>
@@ -5180,9 +5970,12 @@
       <c r="E255" s="1">
         <v>7</v>
       </c>
-      <c r="F255" s="1"/>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F255" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G255" s="1"/>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="2">
         <v>45838</v>
       </c>
@@ -5198,9 +5991,12 @@
       <c r="E256" s="1">
         <v>3</v>
       </c>
-      <c r="F256" s="1"/>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F256" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G256" s="1"/>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="2">
         <v>45838</v>
       </c>
@@ -5216,9 +6012,12 @@
       <c r="E257" s="1">
         <v>5</v>
       </c>
-      <c r="F257" s="1"/>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F257" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G257" s="1"/>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="2">
         <v>45838</v>
       </c>
@@ -5234,9 +6033,12 @@
       <c r="E258" s="1">
         <v>9</v>
       </c>
-      <c r="F258" s="1"/>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F258" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G258" s="1"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="2">
         <v>45838</v>
       </c>
@@ -5252,9 +6054,12 @@
       <c r="E259" s="1">
         <v>2</v>
       </c>
-      <c r="F259" s="1"/>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F259" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G259" s="1"/>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="2">
         <v>45838</v>
       </c>
@@ -5270,9 +6075,12 @@
       <c r="E260" s="1">
         <v>1</v>
       </c>
-      <c r="F260" s="1"/>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F260" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G260" s="1"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="2">
         <v>45838</v>
       </c>
@@ -5288,9 +6096,12 @@
       <c r="E261" s="1">
         <v>5</v>
       </c>
-      <c r="F261" s="1"/>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F261" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G261" s="1"/>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="2">
         <v>45838</v>
       </c>
@@ -5306,9 +6117,12 @@
       <c r="E262" s="1">
         <v>2</v>
       </c>
-      <c r="F262" s="1"/>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F262" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G262" s="1"/>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="2">
         <v>45838</v>
       </c>
@@ -5324,9 +6138,12 @@
       <c r="E263" s="1">
         <v>5</v>
       </c>
-      <c r="F263" s="1"/>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F263" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G263" s="1"/>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="2">
         <v>45838</v>
       </c>
@@ -5342,9 +6159,12 @@
       <c r="E264" s="1">
         <v>2</v>
       </c>
-      <c r="F264" s="1"/>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F264" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G264" s="1"/>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="2">
         <v>45838</v>
       </c>
@@ -5360,9 +6180,12 @@
       <c r="E265" s="1">
         <v>4</v>
       </c>
-      <c r="F265" s="1"/>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F265" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G265" s="1"/>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="2">
         <v>45838</v>
       </c>
@@ -5378,9 +6201,12 @@
       <c r="E266" s="1">
         <v>4</v>
       </c>
-      <c r="F266" s="1"/>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F266" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G266" s="1"/>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="2">
         <v>45838</v>
       </c>
@@ -5396,9 +6222,12 @@
       <c r="E267" s="1">
         <v>2</v>
       </c>
-      <c r="F267" s="1"/>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F267" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G267" s="1"/>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="2">
         <v>45838</v>
       </c>
@@ -5414,9 +6243,12 @@
       <c r="E268" s="1">
         <v>1</v>
       </c>
-      <c r="F268" s="1"/>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F268" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G268" s="1"/>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="2">
         <v>45838</v>
       </c>
@@ -5432,9 +6264,12 @@
       <c r="E269" s="1">
         <v>1</v>
       </c>
-      <c r="F269" s="1"/>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F269" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G269" s="1"/>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="2">
         <v>45838</v>
       </c>
@@ -5450,9 +6285,12 @@
       <c r="E270" s="1">
         <v>3</v>
       </c>
-      <c r="F270" s="1"/>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F270" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G270" s="1"/>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="2">
         <v>45838</v>
       </c>
@@ -5468,9 +6306,12 @@
       <c r="E271" s="1">
         <v>5</v>
       </c>
-      <c r="F271" s="1"/>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F271" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G271" s="1"/>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="2">
         <v>45838</v>
       </c>
@@ -5486,9 +6327,12 @@
       <c r="E272" s="1">
         <v>0</v>
       </c>
-      <c r="F272" s="1"/>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F272" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G272" s="1"/>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="2">
         <v>45838</v>
       </c>
@@ -5504,9 +6348,12 @@
       <c r="E273" s="1">
         <v>4</v>
       </c>
-      <c r="F273" s="1"/>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F273" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G273" s="1"/>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="2">
         <v>45838</v>
       </c>
@@ -5522,9 +6369,12 @@
       <c r="E274" s="1">
         <v>1</v>
       </c>
-      <c r="F274" s="1"/>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F274" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G274" s="1"/>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="2">
         <v>45838</v>
       </c>
@@ -5540,9 +6390,12 @@
       <c r="E275" s="1">
         <v>1</v>
       </c>
-      <c r="F275" s="1"/>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F275" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G275" s="1"/>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="2">
         <v>45838</v>
       </c>
@@ -5558,9 +6411,12 @@
       <c r="E276" s="1">
         <v>1</v>
       </c>
-      <c r="F276" s="1"/>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F276" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G276" s="1"/>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="2">
         <v>45838</v>
       </c>
@@ -5576,9 +6432,12 @@
       <c r="E277" s="1">
         <v>1</v>
       </c>
-      <c r="F277" s="1"/>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F277" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G277" s="1"/>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="2">
         <v>45838</v>
       </c>
@@ -5594,9 +6453,12 @@
       <c r="E278" s="1">
         <v>1</v>
       </c>
-      <c r="F278" s="1"/>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F278" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G278" s="1"/>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="2">
         <v>45838</v>
       </c>
@@ -5612,9 +6474,12 @@
       <c r="E279" s="1">
         <v>1</v>
       </c>
-      <c r="F279" s="1"/>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F279" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G279" s="1"/>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="2">
         <v>45838</v>
       </c>
@@ -5630,9 +6495,12 @@
       <c r="E280" s="1">
         <v>4</v>
       </c>
-      <c r="F280" s="1"/>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F280" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G280" s="1"/>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="2">
         <v>45838</v>
       </c>
@@ -5648,9 +6516,12 @@
       <c r="E281" s="1">
         <v>2</v>
       </c>
-      <c r="F281" s="1"/>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F281" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G281" s="1"/>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="2">
         <v>45838</v>
       </c>
@@ -5666,9 +6537,12 @@
       <c r="E282" s="1">
         <v>12</v>
       </c>
-      <c r="F282" s="1"/>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F282" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G282" s="1"/>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="2">
         <v>45838</v>
       </c>
@@ -5684,9 +6558,12 @@
       <c r="E283" s="1">
         <v>7</v>
       </c>
-      <c r="F283" s="1"/>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F283" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G283" s="1"/>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="2">
         <v>45838</v>
       </c>
@@ -5702,9 +6579,12 @@
       <c r="E284" s="1">
         <v>5</v>
       </c>
-      <c r="F284" s="1"/>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F284" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G284" s="1"/>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="2">
         <v>45838</v>
       </c>
@@ -5720,9 +6600,12 @@
       <c r="E285" s="1">
         <v>6</v>
       </c>
-      <c r="F285" s="1"/>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F285" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G285" s="1"/>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="2">
         <v>45838</v>
       </c>
@@ -5738,9 +6621,12 @@
       <c r="E286" s="1">
         <v>4</v>
       </c>
-      <c r="F286" s="1"/>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F286" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G286" s="1"/>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="2">
         <v>45838</v>
       </c>
@@ -5756,9 +6642,12 @@
       <c r="E287" s="1">
         <v>7</v>
       </c>
-      <c r="F287" s="1"/>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F287" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G287" s="1"/>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="2">
         <v>45838</v>
       </c>
@@ -5774,9 +6663,12 @@
       <c r="E288" s="1">
         <v>3</v>
       </c>
-      <c r="F288" s="1"/>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F288" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G288" s="1"/>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="2">
         <v>45838</v>
       </c>
@@ -5792,9 +6684,12 @@
       <c r="E289" s="1">
         <v>5</v>
       </c>
-      <c r="F289" s="1"/>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F289" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G289" s="1"/>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="2">
         <v>45838</v>
       </c>
@@ -5810,9 +6705,12 @@
       <c r="E290" s="1">
         <v>5</v>
       </c>
-      <c r="F290" s="1"/>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F290" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G290" s="1"/>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="2">
         <v>45838</v>
       </c>
@@ -5828,9 +6726,12 @@
       <c r="E291" s="1">
         <v>5</v>
       </c>
-      <c r="F291" s="1"/>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F291" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G291" s="1"/>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="2">
         <v>45838</v>
       </c>
@@ -5846,9 +6747,12 @@
       <c r="E292" s="1">
         <v>6</v>
       </c>
-      <c r="F292" s="1"/>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F292" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G292" s="1"/>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" s="2">
         <v>45838</v>
       </c>
@@ -5864,9 +6768,12 @@
       <c r="E293" s="1">
         <v>3</v>
       </c>
-      <c r="F293" s="1"/>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F293" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G293" s="1"/>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="2">
         <v>45838</v>
       </c>
@@ -5882,9 +6789,12 @@
       <c r="E294" s="1">
         <v>8</v>
       </c>
-      <c r="F294" s="1"/>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F294" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G294" s="1"/>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="2">
         <v>45838</v>
       </c>
@@ -5900,9 +6810,12 @@
       <c r="E295" s="1">
         <v>4</v>
       </c>
-      <c r="F295" s="1"/>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F295" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G295" s="1"/>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="2">
         <v>45838</v>
       </c>
@@ -5918,9 +6831,12 @@
       <c r="E296" s="1">
         <v>1</v>
       </c>
-      <c r="F296" s="1"/>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F296" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G296" s="1"/>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="2">
         <v>45838</v>
       </c>
@@ -5936,9 +6852,12 @@
       <c r="E297" s="1">
         <v>4</v>
       </c>
-      <c r="F297" s="1"/>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F297" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G297" s="1"/>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="2">
         <v>45838</v>
       </c>
@@ -5954,9 +6873,12 @@
       <c r="E298" s="1">
         <v>3</v>
       </c>
-      <c r="F298" s="1"/>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F298" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G298" s="1"/>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="2">
         <v>45838</v>
       </c>
@@ -5972,9 +6894,12 @@
       <c r="E299" s="1">
         <v>8</v>
       </c>
-      <c r="F299" s="1"/>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F299" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G299" s="1"/>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="2">
         <v>45838</v>
       </c>
@@ -5990,9 +6915,12 @@
       <c r="E300" s="1">
         <v>11</v>
       </c>
-      <c r="F300" s="1"/>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F300" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G300" s="1"/>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="2">
         <v>45838</v>
       </c>
@@ -6008,9 +6936,12 @@
       <c r="E301" s="1">
         <v>7</v>
       </c>
-      <c r="F301" s="1"/>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F301" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G301" s="1"/>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="2">
         <v>45854</v>
       </c>
@@ -6026,9 +6957,12 @@
       <c r="E302" s="1">
         <v>0</v>
       </c>
-      <c r="F302" s="1"/>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F302" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G302" s="1"/>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" s="2">
         <v>45854</v>
       </c>
@@ -6044,9 +6978,12 @@
       <c r="E303" s="1">
         <v>0</v>
       </c>
-      <c r="F303" s="1"/>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F303" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G303" s="1"/>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" s="2">
         <v>45854</v>
       </c>
@@ -6062,9 +6999,12 @@
       <c r="E304" s="1">
         <v>0</v>
       </c>
-      <c r="F304" s="1"/>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F304" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G304" s="1"/>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="2">
         <v>45854</v>
       </c>
@@ -6080,9 +7020,12 @@
       <c r="E305" s="1">
         <v>0</v>
       </c>
-      <c r="F305" s="1"/>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F305" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G305" s="1"/>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" s="2">
         <v>45854</v>
       </c>
@@ -6098,9 +7041,12 @@
       <c r="E306" s="1">
         <v>0</v>
       </c>
-      <c r="F306" s="1"/>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F306" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G306" s="1"/>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" s="2">
         <v>45854</v>
       </c>
@@ -6116,9 +7062,12 @@
       <c r="E307" s="1">
         <v>0</v>
       </c>
-      <c r="F307" s="1"/>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F307" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G307" s="1"/>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" s="2">
         <v>45854</v>
       </c>
@@ -6134,9 +7083,12 @@
       <c r="E308" s="1">
         <v>0</v>
       </c>
-      <c r="F308" s="1"/>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F308" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G308" s="1"/>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" s="2">
         <v>45854</v>
       </c>
@@ -6152,9 +7104,12 @@
       <c r="E309" s="1">
         <v>1</v>
       </c>
-      <c r="F309" s="1"/>
-    </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F309" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G309" s="1"/>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310" s="2">
         <v>45854</v>
       </c>
@@ -6170,9 +7125,12 @@
       <c r="E310" s="1">
         <v>0</v>
       </c>
-      <c r="F310" s="1"/>
-    </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F310" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G310" s="1"/>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" s="2">
         <v>45854</v>
       </c>
@@ -6188,9 +7146,12 @@
       <c r="E311" s="1">
         <v>0</v>
       </c>
-      <c r="F311" s="1"/>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F311" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G311" s="1"/>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312" s="2">
         <v>45854</v>
       </c>
@@ -6206,9 +7167,12 @@
       <c r="E312" s="1">
         <v>0</v>
       </c>
-      <c r="F312" s="1"/>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F312" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G312" s="1"/>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313" s="2">
         <v>45854</v>
       </c>
@@ -6224,9 +7188,12 @@
       <c r="E313" s="1">
         <v>0</v>
       </c>
-      <c r="F313" s="1"/>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F313" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G313" s="1"/>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" s="2">
         <v>45854</v>
       </c>
@@ -6242,9 +7209,12 @@
       <c r="E314" s="1">
         <v>0</v>
       </c>
-      <c r="F314" s="1"/>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F314" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G314" s="1"/>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" s="2">
         <v>45854</v>
       </c>
@@ -6260,9 +7230,12 @@
       <c r="E315" s="1">
         <v>0</v>
       </c>
-      <c r="F315" s="1"/>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F315" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G315" s="1"/>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316" s="2">
         <v>45854</v>
       </c>
@@ -6278,9 +7251,12 @@
       <c r="E316" s="1">
         <v>0</v>
       </c>
-      <c r="F316" s="1"/>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F316" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G316" s="1"/>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" s="2">
         <v>45854</v>
       </c>
@@ -6296,9 +7272,12 @@
       <c r="E317" s="1">
         <v>0</v>
       </c>
-      <c r="F317" s="1"/>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F317" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G317" s="1"/>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318" s="2">
         <v>45854</v>
       </c>
@@ -6314,9 +7293,12 @@
       <c r="E318" s="1">
         <v>0</v>
       </c>
-      <c r="F318" s="1"/>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F318" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G318" s="1"/>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" s="2">
         <v>45854</v>
       </c>
@@ -6332,9 +7314,12 @@
       <c r="E319" s="1">
         <v>0</v>
       </c>
-      <c r="F319" s="1"/>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F319" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G319" s="1"/>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" s="2">
         <v>45854</v>
       </c>
@@ -6350,9 +7335,12 @@
       <c r="E320" s="1">
         <v>0</v>
       </c>
-      <c r="F320" s="1"/>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F320" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G320" s="1"/>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321" s="2">
         <v>45854</v>
       </c>
@@ -6368,9 +7356,12 @@
       <c r="E321" s="1">
         <v>0</v>
       </c>
-      <c r="F321" s="1"/>
-    </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F321" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G321" s="1"/>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322" s="2">
         <v>45854</v>
       </c>
@@ -6386,9 +7377,12 @@
       <c r="E322" s="1">
         <v>0</v>
       </c>
-      <c r="F322" s="1"/>
-    </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F322" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G322" s="1"/>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323" s="2">
         <v>45854</v>
       </c>
@@ -6404,9 +7398,12 @@
       <c r="E323" s="1">
         <v>0</v>
       </c>
-      <c r="F323" s="1"/>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F323" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G323" s="1"/>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324" s="2">
         <v>45854</v>
       </c>
@@ -6422,9 +7419,12 @@
       <c r="E324" s="1">
         <v>1</v>
       </c>
-      <c r="F324" s="1"/>
-    </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F324" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G324" s="1"/>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325" s="2">
         <v>45854</v>
       </c>
@@ -6440,9 +7440,12 @@
       <c r="E325" s="1">
         <v>0</v>
       </c>
-      <c r="F325" s="1"/>
-    </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F325" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G325" s="1"/>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326" s="2">
         <v>45854</v>
       </c>
@@ -6458,9 +7461,12 @@
       <c r="E326" s="1">
         <v>0</v>
       </c>
-      <c r="F326" s="1"/>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F326" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G326" s="1"/>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327" s="2">
         <v>45854</v>
       </c>
@@ -6476,9 +7482,12 @@
       <c r="E327" s="1">
         <v>0</v>
       </c>
-      <c r="F327" s="1"/>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F327" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G327" s="1"/>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328" s="2">
         <v>45854</v>
       </c>
@@ -6494,9 +7503,12 @@
       <c r="E328" s="1">
         <v>0</v>
       </c>
-      <c r="F328" s="1"/>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F328" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G328" s="1"/>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329" s="2">
         <v>45854</v>
       </c>
@@ -6512,9 +7524,12 @@
       <c r="E329" s="1">
         <v>0</v>
       </c>
-      <c r="F329" s="1"/>
-    </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F329" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G329" s="1"/>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330" s="2">
         <v>45854</v>
       </c>
@@ -6530,9 +7545,12 @@
       <c r="E330" s="1">
         <v>0</v>
       </c>
-      <c r="F330" s="1"/>
-    </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F330" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G330" s="1"/>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331" s="2">
         <v>45854</v>
       </c>
@@ -6548,9 +7566,12 @@
       <c r="E331" s="1">
         <v>1</v>
       </c>
-      <c r="F331" s="1"/>
-    </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F331" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G331" s="1"/>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332" s="2">
         <v>45854</v>
       </c>
@@ -6566,9 +7587,12 @@
       <c r="E332" s="1">
         <v>0</v>
       </c>
-      <c r="F332" s="1"/>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F332" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G332" s="1"/>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333" s="2">
         <v>45854</v>
       </c>
@@ -6584,9 +7608,12 @@
       <c r="E333" s="1">
         <v>0</v>
       </c>
-      <c r="F333" s="1"/>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F333" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G333" s="1"/>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334" s="2">
         <v>45854</v>
       </c>
@@ -6602,9 +7629,12 @@
       <c r="E334" s="1">
         <v>0</v>
       </c>
-      <c r="F334" s="1"/>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F334" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G334" s="1"/>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335" s="2">
         <v>45854</v>
       </c>
@@ -6620,9 +7650,12 @@
       <c r="E335" s="1">
         <v>0</v>
       </c>
-      <c r="F335" s="1"/>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F335" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G335" s="1"/>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336" s="2">
         <v>45854</v>
       </c>
@@ -6638,9 +7671,12 @@
       <c r="E336" s="1">
         <v>0</v>
       </c>
-      <c r="F336" s="1"/>
-    </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F336" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G336" s="1"/>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337" s="2">
         <v>45854</v>
       </c>
@@ -6656,9 +7692,12 @@
       <c r="E337" s="1">
         <v>0</v>
       </c>
-      <c r="F337" s="1"/>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F337" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G337" s="1"/>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338" s="2">
         <v>45854</v>
       </c>
@@ -6674,9 +7713,12 @@
       <c r="E338" s="1">
         <v>1</v>
       </c>
-      <c r="F338" s="1"/>
-    </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F338" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G338" s="1"/>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339" s="2">
         <v>45854</v>
       </c>
@@ -6692,9 +7734,12 @@
       <c r="E339" s="1">
         <v>0</v>
       </c>
-      <c r="F339" s="1"/>
-    </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F339" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G339" s="1"/>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340" s="2">
         <v>45854</v>
       </c>
@@ -6710,9 +7755,12 @@
       <c r="E340" s="1">
         <v>0</v>
       </c>
-      <c r="F340" s="1"/>
-    </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F340" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G340" s="1"/>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341" s="2">
         <v>45854</v>
       </c>
@@ -6728,9 +7776,12 @@
       <c r="E341" s="1">
         <v>1</v>
       </c>
-      <c r="F341" s="1"/>
-    </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F341" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G341" s="1"/>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342" s="2">
         <v>45854</v>
       </c>
@@ -6746,9 +7797,12 @@
       <c r="E342" s="1">
         <v>0</v>
       </c>
-      <c r="F342" s="1"/>
-    </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F342" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G342" s="1"/>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343" s="2">
         <v>45854</v>
       </c>
@@ -6764,9 +7818,12 @@
       <c r="E343" s="1">
         <v>0</v>
       </c>
-      <c r="F343" s="1"/>
-    </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F343" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G343" s="1"/>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344" s="2">
         <v>45854</v>
       </c>
@@ -6782,9 +7839,12 @@
       <c r="E344" s="1">
         <v>0</v>
       </c>
-      <c r="F344" s="1"/>
-    </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F344" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G344" s="1"/>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345" s="2">
         <v>45854</v>
       </c>
@@ -6800,9 +7860,12 @@
       <c r="E345" s="1">
         <v>0</v>
       </c>
-      <c r="F345" s="1"/>
-    </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F345" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G345" s="1"/>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346" s="2">
         <v>45854</v>
       </c>
@@ -6818,9 +7881,12 @@
       <c r="E346" s="1">
         <v>0</v>
       </c>
-      <c r="F346" s="1"/>
-    </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F346" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G346" s="1"/>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347" s="2">
         <v>45854</v>
       </c>
@@ -6836,9 +7902,12 @@
       <c r="E347" s="1">
         <v>1</v>
       </c>
-      <c r="F347" s="1"/>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F347" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G347" s="1"/>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348" s="2">
         <v>45854</v>
       </c>
@@ -6854,9 +7923,12 @@
       <c r="E348" s="1">
         <v>1</v>
       </c>
-      <c r="F348" s="1"/>
-    </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F348" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G348" s="1"/>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349" s="2">
         <v>45854</v>
       </c>
@@ -6871,10 +7943,13 @@
       </c>
       <c r="E349" s="1"/>
       <c r="F349" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G349" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350" s="2">
         <v>45854</v>
       </c>
@@ -6890,9 +7965,12 @@
       <c r="E350" s="1">
         <v>0</v>
       </c>
-      <c r="F350" s="1"/>
-    </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F350" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G350" s="1"/>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351" s="2">
         <v>45854</v>
       </c>
@@ -6908,9 +7986,12 @@
       <c r="E351" s="1">
         <v>0</v>
       </c>
-      <c r="F351" s="1"/>
-    </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F351" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G351" s="1"/>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352" s="2">
         <v>45854</v>
       </c>
@@ -6926,9 +8007,12 @@
       <c r="E352" s="1">
         <v>1</v>
       </c>
-      <c r="F352" s="1"/>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F352" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G352" s="1"/>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353" s="2">
         <v>45854</v>
       </c>
@@ -6944,9 +8028,12 @@
       <c r="E353" s="1">
         <v>0</v>
       </c>
-      <c r="F353" s="1"/>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F353" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G353" s="1"/>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A354" s="2">
         <v>45854</v>
       </c>
@@ -6962,9 +8049,12 @@
       <c r="E354" s="1">
         <v>1</v>
       </c>
-      <c r="F354" s="1"/>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F354" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G354" s="1"/>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A355" s="2">
         <v>45854</v>
       </c>
@@ -6980,9 +8070,12 @@
       <c r="E355" s="1">
         <v>1</v>
       </c>
-      <c r="F355" s="1"/>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F355" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G355" s="1"/>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A356" s="2">
         <v>45854</v>
       </c>
@@ -6998,9 +8091,12 @@
       <c r="E356" s="1">
         <v>0</v>
       </c>
-      <c r="F356" s="1"/>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F356" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G356" s="1"/>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A357" s="2">
         <v>45854</v>
       </c>
@@ -7016,9 +8112,12 @@
       <c r="E357" s="1">
         <v>1</v>
       </c>
-      <c r="F357" s="1"/>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F357" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G357" s="1"/>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A358" s="2">
         <v>45854</v>
       </c>
@@ -7034,9 +8133,12 @@
       <c r="E358" s="1">
         <v>0</v>
       </c>
-      <c r="F358" s="1"/>
-    </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F358" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G358" s="1"/>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A359" s="2">
         <v>45854</v>
       </c>
@@ -7052,9 +8154,12 @@
       <c r="E359" s="1">
         <v>0</v>
       </c>
-      <c r="F359" s="1"/>
-    </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F359" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G359" s="1"/>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A360" s="2">
         <v>45854</v>
       </c>
@@ -7070,9 +8175,12 @@
       <c r="E360" s="1">
         <v>0</v>
       </c>
-      <c r="F360" s="1"/>
-    </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F360" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G360" s="1"/>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361" s="2">
         <v>45854</v>
       </c>
@@ -7088,9 +8196,12 @@
       <c r="E361" s="1">
         <v>0</v>
       </c>
-      <c r="F361" s="1"/>
-    </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F361" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G361" s="1"/>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362" s="2">
         <v>45854</v>
       </c>
@@ -7106,9 +8217,12 @@
       <c r="E362" s="1">
         <v>0</v>
       </c>
-      <c r="F362" s="1"/>
-    </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F362" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G362" s="1"/>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A363" s="2">
         <v>45854</v>
       </c>
@@ -7124,9 +8238,12 @@
       <c r="E363" s="1">
         <v>3</v>
       </c>
-      <c r="F363" s="1"/>
-    </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F363" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G363" s="1"/>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A364" s="2">
         <v>45854</v>
       </c>
@@ -7142,9 +8259,12 @@
       <c r="E364" s="1">
         <v>0</v>
       </c>
-      <c r="F364" s="1"/>
-    </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F364" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G364" s="1"/>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365" s="2">
         <v>45854</v>
       </c>
@@ -7160,9 +8280,12 @@
       <c r="E365" s="1">
         <v>0</v>
       </c>
-      <c r="F365" s="1"/>
-    </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F365" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G365" s="1"/>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A366" s="2">
         <v>45854</v>
       </c>
@@ -7178,9 +8301,12 @@
       <c r="E366" s="1">
         <v>0</v>
       </c>
-      <c r="F366" s="1"/>
-    </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F366" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G366" s="1"/>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A367" s="2">
         <v>45854</v>
       </c>
@@ -7196,9 +8322,12 @@
       <c r="E367" s="1">
         <v>0</v>
       </c>
-      <c r="F367" s="1"/>
-    </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F367" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G367" s="1"/>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A368" s="2">
         <v>45854</v>
       </c>
@@ -7214,9 +8343,12 @@
       <c r="E368" s="1">
         <v>0</v>
       </c>
-      <c r="F368" s="1"/>
-    </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F368" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G368" s="1"/>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A369" s="2">
         <v>45854</v>
       </c>
@@ -7232,9 +8364,12 @@
       <c r="E369" s="1">
         <v>0</v>
       </c>
-      <c r="F369" s="1"/>
-    </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F369" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G369" s="1"/>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A370" s="2">
         <v>45854</v>
       </c>
@@ -7250,9 +8385,12 @@
       <c r="E370" s="1">
         <v>0</v>
       </c>
-      <c r="F370" s="1"/>
-    </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F370" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G370" s="1"/>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A371" s="2">
         <v>45854</v>
       </c>
@@ -7268,9 +8406,12 @@
       <c r="E371" s="1">
         <v>0</v>
       </c>
-      <c r="F371" s="1"/>
-    </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F371" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G371" s="1"/>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A372" s="2">
         <v>45854</v>
       </c>
@@ -7286,9 +8427,12 @@
       <c r="E372" s="1">
         <v>2</v>
       </c>
-      <c r="F372" s="1"/>
-    </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F372" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G372" s="1"/>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A373" s="2">
         <v>45854</v>
       </c>
@@ -7304,9 +8448,12 @@
       <c r="E373" s="1">
         <v>0</v>
       </c>
-      <c r="F373" s="1"/>
-    </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F373" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G373" s="1"/>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374" s="2">
         <v>45854</v>
       </c>
@@ -7322,9 +8469,12 @@
       <c r="E374" s="1">
         <v>0</v>
       </c>
-      <c r="F374" s="1"/>
-    </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F374" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G374" s="1"/>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375" s="2">
         <v>45854</v>
       </c>
@@ -7340,9 +8490,12 @@
       <c r="E375" s="1">
         <v>0</v>
       </c>
-      <c r="F375" s="1"/>
-    </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F375" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G375" s="1"/>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376" s="2">
         <v>45854</v>
       </c>
@@ -7358,9 +8511,12 @@
       <c r="E376" s="1">
         <v>0</v>
       </c>
-      <c r="F376" s="1"/>
-    </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F376" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G376" s="1"/>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377" s="2">
         <v>45854</v>
       </c>
@@ -7376,9 +8532,12 @@
       <c r="E377" s="1">
         <v>0</v>
       </c>
-      <c r="F377" s="1"/>
-    </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F377" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G377" s="1"/>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A378" s="2">
         <v>45854</v>
       </c>
@@ -7394,9 +8553,12 @@
       <c r="E378" s="1">
         <v>1</v>
       </c>
-      <c r="F378" s="1"/>
-    </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F378" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G378" s="1"/>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379" s="2">
         <v>45854</v>
       </c>
@@ -7412,9 +8574,12 @@
       <c r="E379" s="1">
         <v>1</v>
       </c>
-      <c r="F379" s="1"/>
-    </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F379" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G379" s="1"/>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380" s="2">
         <v>45854</v>
       </c>
@@ -7430,9 +8595,12 @@
       <c r="E380" s="1">
         <v>0</v>
       </c>
-      <c r="F380" s="1"/>
-    </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F380" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G380" s="1"/>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A381" s="2">
         <v>45854</v>
       </c>
@@ -7448,9 +8616,12 @@
       <c r="E381" s="1">
         <v>0</v>
       </c>
-      <c r="F381" s="1"/>
-    </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F381" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G381" s="1"/>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A382" s="2">
         <v>45854</v>
       </c>
@@ -7466,9 +8637,12 @@
       <c r="E382" s="1">
         <v>0</v>
       </c>
-      <c r="F382" s="1"/>
-    </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F382" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G382" s="1"/>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A383" s="2">
         <v>45854</v>
       </c>
@@ -7484,9 +8658,12 @@
       <c r="E383" s="1">
         <v>1</v>
       </c>
-      <c r="F383" s="1"/>
-    </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F383" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G383" s="1"/>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A384" s="2">
         <v>45854</v>
       </c>
@@ -7502,9 +8679,12 @@
       <c r="E384" s="1">
         <v>0</v>
       </c>
-      <c r="F384" s="1"/>
-    </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F384" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G384" s="1"/>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385" s="2">
         <v>45854</v>
       </c>
@@ -7520,9 +8700,12 @@
       <c r="E385" s="1">
         <v>1</v>
       </c>
-      <c r="F385" s="1"/>
-    </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F385" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G385" s="1"/>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386" s="2">
         <v>45854</v>
       </c>
@@ -7538,9 +8721,12 @@
       <c r="E386" s="1">
         <v>0</v>
       </c>
-      <c r="F386" s="1"/>
-    </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F386" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G386" s="1"/>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387" s="2">
         <v>45854</v>
       </c>
@@ -7556,9 +8742,12 @@
       <c r="E387" s="1">
         <v>0</v>
       </c>
-      <c r="F387" s="1"/>
-    </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F387" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G387" s="1"/>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388" s="2">
         <v>45854</v>
       </c>
@@ -7574,9 +8763,12 @@
       <c r="E388" s="1">
         <v>1</v>
       </c>
-      <c r="F388" s="1"/>
-    </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F388" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G388" s="1"/>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A389" s="2">
         <v>45854</v>
       </c>
@@ -7592,9 +8784,12 @@
       <c r="E389" s="1">
         <v>0</v>
       </c>
-      <c r="F389" s="1"/>
-    </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F389" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G389" s="1"/>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A390" s="2">
         <v>45854</v>
       </c>
@@ -7610,9 +8805,12 @@
       <c r="E390" s="1">
         <v>0</v>
       </c>
-      <c r="F390" s="1"/>
-    </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F390" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G390" s="1"/>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A391" s="2">
         <v>45854</v>
       </c>
@@ -7628,9 +8826,12 @@
       <c r="E391" s="1">
         <v>0</v>
       </c>
-      <c r="F391" s="1"/>
-    </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F391" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G391" s="1"/>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A392" s="2">
         <v>45854</v>
       </c>
@@ -7646,9 +8847,12 @@
       <c r="E392" s="1">
         <v>0</v>
       </c>
-      <c r="F392" s="1"/>
-    </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F392" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G392" s="1"/>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A393" s="2">
         <v>45854</v>
       </c>
@@ -7664,9 +8868,12 @@
       <c r="E393" s="1">
         <v>0</v>
       </c>
-      <c r="F393" s="1"/>
-    </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F393" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G393" s="1"/>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A394" s="2">
         <v>45854</v>
       </c>
@@ -7682,9 +8889,12 @@
       <c r="E394" s="1">
         <v>0</v>
       </c>
-      <c r="F394" s="1"/>
-    </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F394" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G394" s="1"/>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A395" s="2">
         <v>45854</v>
       </c>
@@ -7700,9 +8910,12 @@
       <c r="E395" s="1">
         <v>0</v>
       </c>
-      <c r="F395" s="1"/>
-    </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F395" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G395" s="1"/>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A396" s="2">
         <v>45854</v>
       </c>
@@ -7718,9 +8931,12 @@
       <c r="E396" s="1">
         <v>0</v>
       </c>
-      <c r="F396" s="1"/>
-    </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F396" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G396" s="1"/>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A397" s="2">
         <v>45854</v>
       </c>
@@ -7736,9 +8952,12 @@
       <c r="E397" s="1">
         <v>2</v>
       </c>
-      <c r="F397" s="1"/>
-    </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F397" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G397" s="1"/>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A398" s="2">
         <v>45854</v>
       </c>
@@ -7754,9 +8973,12 @@
       <c r="E398" s="1">
         <v>2</v>
       </c>
-      <c r="F398" s="1"/>
-    </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F398" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G398" s="1"/>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A399" s="2">
         <v>45854</v>
       </c>
@@ -7772,9 +8994,12 @@
       <c r="E399" s="1">
         <v>0</v>
       </c>
-      <c r="F399" s="1"/>
-    </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F399" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G399" s="1"/>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A400" s="2">
         <v>45854</v>
       </c>
@@ -7790,9 +9015,12 @@
       <c r="E400" s="1">
         <v>0</v>
       </c>
-      <c r="F400" s="1"/>
-    </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F400" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G400" s="1"/>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A401" s="2">
         <v>45854</v>
       </c>
@@ -7808,9 +9036,12 @@
       <c r="E401" s="1">
         <v>0</v>
       </c>
-      <c r="F401" s="1"/>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F401" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G401" s="1"/>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A402" s="2">
         <v>45867</v>
       </c>
@@ -7826,9 +9057,12 @@
       <c r="E402" s="1">
         <v>0</v>
       </c>
-      <c r="F402" s="1"/>
-    </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F402" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G402" s="1"/>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A403" s="2">
         <v>45867</v>
       </c>
@@ -7844,9 +9078,12 @@
       <c r="E403" s="1">
         <v>0</v>
       </c>
-      <c r="F403" s="1"/>
-    </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F403" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G403" s="1"/>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A404" s="2">
         <v>45867</v>
       </c>
@@ -7862,9 +9099,12 @@
       <c r="E404" s="1">
         <v>1</v>
       </c>
-      <c r="F404" s="1"/>
-    </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F404" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G404" s="1"/>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A405" s="2">
         <v>45867</v>
       </c>
@@ -7880,9 +9120,12 @@
       <c r="E405" s="1">
         <v>1</v>
       </c>
-      <c r="F405" s="1"/>
-    </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F405" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G405" s="1"/>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A406" s="2">
         <v>45867</v>
       </c>
@@ -7898,9 +9141,12 @@
       <c r="E406" s="1">
         <v>0</v>
       </c>
-      <c r="F406" s="1"/>
-    </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F406" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G406" s="1"/>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A407" s="2">
         <v>45867</v>
       </c>
@@ -7916,9 +9162,12 @@
       <c r="E407" s="1">
         <v>0</v>
       </c>
-      <c r="F407" s="1"/>
-    </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F407" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G407" s="1"/>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A408" s="2">
         <v>45867</v>
       </c>
@@ -7934,9 +9183,12 @@
       <c r="E408" s="1">
         <v>0</v>
       </c>
-      <c r="F408" s="1"/>
-    </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F408" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G408" s="1"/>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A409" s="2">
         <v>45867</v>
       </c>
@@ -7952,9 +9204,12 @@
       <c r="E409" s="1">
         <v>1</v>
       </c>
-      <c r="F409" s="1"/>
-    </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F409" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G409" s="1"/>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A410" s="2">
         <v>45867</v>
       </c>
@@ -7970,9 +9225,12 @@
       <c r="E410" s="1">
         <v>1</v>
       </c>
-      <c r="F410" s="1"/>
-    </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F410" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G410" s="1"/>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A411" s="2">
         <v>45867</v>
       </c>
@@ -7988,9 +9246,12 @@
       <c r="E411" s="1">
         <v>0</v>
       </c>
-      <c r="F411" s="1"/>
-    </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F411" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G411" s="1"/>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A412" s="2">
         <v>45867</v>
       </c>
@@ -8006,9 +9267,12 @@
       <c r="E412" s="1">
         <v>0</v>
       </c>
-      <c r="F412" s="1"/>
-    </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F412" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G412" s="1"/>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A413" s="2">
         <v>45867</v>
       </c>
@@ -8024,9 +9288,12 @@
       <c r="E413" s="1">
         <v>0</v>
       </c>
-      <c r="F413" s="1"/>
-    </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F413" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G413" s="1"/>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A414" s="2">
         <v>45867</v>
       </c>
@@ -8042,9 +9309,12 @@
       <c r="E414" s="1">
         <v>1</v>
       </c>
-      <c r="F414" s="1"/>
-    </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F414" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G414" s="1"/>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A415" s="2">
         <v>45867</v>
       </c>
@@ -8060,9 +9330,12 @@
       <c r="E415" s="1">
         <v>0</v>
       </c>
-      <c r="F415" s="1"/>
-    </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F415" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G415" s="1"/>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A416" s="2">
         <v>45867</v>
       </c>
@@ -8078,9 +9351,12 @@
       <c r="E416" s="1">
         <v>1</v>
       </c>
-      <c r="F416" s="1"/>
-    </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F416" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G416" s="1"/>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A417" s="2">
         <v>45867</v>
       </c>
@@ -8096,9 +9372,12 @@
       <c r="E417" s="1">
         <v>0</v>
       </c>
-      <c r="F417" s="1"/>
-    </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F417" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G417" s="1"/>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A418" s="2">
         <v>45867</v>
       </c>
@@ -8114,9 +9393,12 @@
       <c r="E418" s="1">
         <v>0</v>
       </c>
-      <c r="F418" s="1"/>
-    </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F418" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G418" s="1"/>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A419" s="2">
         <v>45867</v>
       </c>
@@ -8132,9 +9414,12 @@
       <c r="E419" s="1">
         <v>1</v>
       </c>
-      <c r="F419" s="1"/>
-    </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F419" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G419" s="1"/>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A420" s="2">
         <v>45867</v>
       </c>
@@ -8150,9 +9435,12 @@
       <c r="E420" s="1">
         <v>1</v>
       </c>
-      <c r="F420" s="1"/>
-    </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F420" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G420" s="1"/>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A421" s="2">
         <v>45867</v>
       </c>
@@ -8168,9 +9456,12 @@
       <c r="E421" s="1">
         <v>0</v>
       </c>
-      <c r="F421" s="1"/>
-    </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F421" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G421" s="1"/>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A422" s="2">
         <v>45867</v>
       </c>
@@ -8186,9 +9477,12 @@
       <c r="E422" s="1">
         <v>0</v>
       </c>
-      <c r="F422" s="1"/>
-    </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F422" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G422" s="1"/>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A423" s="2">
         <v>45867</v>
       </c>
@@ -8204,9 +9498,12 @@
       <c r="E423" s="1">
         <v>0</v>
       </c>
-      <c r="F423" s="1"/>
-    </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F423" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G423" s="1"/>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A424" s="2">
         <v>45867</v>
       </c>
@@ -8222,9 +9519,12 @@
       <c r="E424" s="1">
         <v>1</v>
       </c>
-      <c r="F424" s="1"/>
-    </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F424" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G424" s="1"/>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A425" s="2">
         <v>45867</v>
       </c>
@@ -8240,9 +9540,12 @@
       <c r="E425" s="1">
         <v>0</v>
       </c>
-      <c r="F425" s="1"/>
-    </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F425" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G425" s="1"/>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A426" s="2">
         <v>45867</v>
       </c>
@@ -8258,9 +9561,12 @@
       <c r="E426" s="1">
         <v>0</v>
       </c>
-      <c r="F426" s="1"/>
-    </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F426" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G426" s="1"/>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A427" s="2">
         <v>45867</v>
       </c>
@@ -8276,9 +9582,12 @@
       <c r="E427" s="1">
         <v>0</v>
       </c>
-      <c r="F427" s="1"/>
-    </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F427" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G427" s="1"/>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A428" s="2">
         <v>45867</v>
       </c>
@@ -8294,9 +9603,12 @@
       <c r="E428" s="1">
         <v>0</v>
       </c>
-      <c r="F428" s="1"/>
-    </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F428" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G428" s="1"/>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A429" s="2">
         <v>45867</v>
       </c>
@@ -8312,9 +9624,12 @@
       <c r="E429" s="1">
         <v>0</v>
       </c>
-      <c r="F429" s="1"/>
-    </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F429" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G429" s="1"/>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A430" s="2">
         <v>45867</v>
       </c>
@@ -8330,9 +9645,12 @@
       <c r="E430" s="1">
         <v>0</v>
       </c>
-      <c r="F430" s="1"/>
-    </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F430" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G430" s="1"/>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A431" s="2">
         <v>45867</v>
       </c>
@@ -8348,9 +9666,12 @@
       <c r="E431" s="1">
         <v>0</v>
       </c>
-      <c r="F431" s="1"/>
-    </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F431" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G431" s="1"/>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A432" s="2">
         <v>45867</v>
       </c>
@@ -8366,9 +9687,12 @@
       <c r="E432" s="1">
         <v>0</v>
       </c>
-      <c r="F432" s="1"/>
-    </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F432" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G432" s="1"/>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A433" s="2">
         <v>45867</v>
       </c>
@@ -8384,9 +9708,12 @@
       <c r="E433" s="1">
         <v>0</v>
       </c>
-      <c r="F433" s="1"/>
-    </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F433" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G433" s="1"/>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A434" s="2">
         <v>45867</v>
       </c>
@@ -8402,9 +9729,12 @@
       <c r="E434" s="1">
         <v>0</v>
       </c>
-      <c r="F434" s="1"/>
-    </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F434" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G434" s="1"/>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A435" s="2">
         <v>45867</v>
       </c>
@@ -8420,9 +9750,12 @@
       <c r="E435" s="1">
         <v>0</v>
       </c>
-      <c r="F435" s="1"/>
-    </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F435" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G435" s="1"/>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A436" s="2">
         <v>45867</v>
       </c>
@@ -8438,9 +9771,12 @@
       <c r="E436" s="1">
         <v>0</v>
       </c>
-      <c r="F436" s="1"/>
-    </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F436" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G436" s="1"/>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A437" s="2">
         <v>45867</v>
       </c>
@@ -8456,9 +9792,12 @@
       <c r="E437" s="1">
         <v>0</v>
       </c>
-      <c r="F437" s="1"/>
-    </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F437" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G437" s="1"/>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A438" s="2">
         <v>45867</v>
       </c>
@@ -8474,9 +9813,12 @@
       <c r="E438" s="1">
         <v>0</v>
       </c>
-      <c r="F438" s="1"/>
-    </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F438" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G438" s="1"/>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A439" s="2">
         <v>45867</v>
       </c>
@@ -8492,9 +9834,12 @@
       <c r="E439" s="1">
         <v>0</v>
       </c>
-      <c r="F439" s="1"/>
-    </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F439" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G439" s="1"/>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A440" s="2">
         <v>45867</v>
       </c>
@@ -8510,9 +9855,12 @@
       <c r="E440" s="1">
         <v>0</v>
       </c>
-      <c r="F440" s="1"/>
-    </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F440" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G440" s="1"/>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A441" s="2">
         <v>45867</v>
       </c>
@@ -8528,9 +9876,12 @@
       <c r="E441" s="1">
         <v>0</v>
       </c>
-      <c r="F441" s="1"/>
-    </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F441" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G441" s="1"/>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A442" s="2">
         <v>45867</v>
       </c>
@@ -8546,9 +9897,12 @@
       <c r="E442" s="1">
         <v>0</v>
       </c>
-      <c r="F442" s="1"/>
-    </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F442" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G442" s="1"/>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A443" s="2">
         <v>45867</v>
       </c>
@@ -8564,9 +9918,12 @@
       <c r="E443" s="1">
         <v>0</v>
       </c>
-      <c r="F443" s="1"/>
-    </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F443" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G443" s="1"/>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A444" s="2">
         <v>45867</v>
       </c>
@@ -8582,9 +9939,12 @@
       <c r="E444" s="1">
         <v>0</v>
       </c>
-      <c r="F444" s="1"/>
-    </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F444" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G444" s="1"/>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A445" s="2">
         <v>45867</v>
       </c>
@@ -8600,9 +9960,12 @@
       <c r="E445" s="1">
         <v>0</v>
       </c>
-      <c r="F445" s="1"/>
-    </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F445" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G445" s="1"/>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A446" s="2">
         <v>45867</v>
       </c>
@@ -8618,9 +9981,12 @@
       <c r="E446" s="1">
         <v>0</v>
       </c>
-      <c r="F446" s="1"/>
-    </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F446" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G446" s="1"/>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A447" s="2">
         <v>45867</v>
       </c>
@@ -8636,9 +10002,12 @@
       <c r="E447" s="1">
         <v>0</v>
       </c>
-      <c r="F447" s="1"/>
-    </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F447" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G447" s="1"/>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A448" s="2">
         <v>45867</v>
       </c>
@@ -8654,9 +10023,12 @@
       <c r="E448" s="1">
         <v>0</v>
       </c>
-      <c r="F448" s="1"/>
-    </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F448" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G448" s="1"/>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A449" s="2">
         <v>45867</v>
       </c>
@@ -8672,9 +10044,12 @@
       <c r="E449" s="1">
         <v>0</v>
       </c>
-      <c r="F449" s="1"/>
-    </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F449" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G449" s="1"/>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A450" s="2">
         <v>45867</v>
       </c>
@@ -8690,9 +10065,12 @@
       <c r="E450" s="1">
         <v>0</v>
       </c>
-      <c r="F450" s="1"/>
-    </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F450" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G450" s="1"/>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A451" s="2">
         <v>45867</v>
       </c>
@@ -8708,9 +10086,12 @@
       <c r="E451" s="1">
         <v>0</v>
       </c>
-      <c r="F451" s="1"/>
-    </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F451" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G451" s="1"/>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A452" s="2">
         <v>45867</v>
       </c>
@@ -8726,9 +10107,12 @@
       <c r="E452" s="1">
         <v>0</v>
       </c>
-      <c r="F452" s="1"/>
-    </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F452" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G452" s="1"/>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A453" s="2">
         <v>45867</v>
       </c>
@@ -8744,9 +10128,12 @@
       <c r="E453" s="1">
         <v>0</v>
       </c>
-      <c r="F453" s="1"/>
-    </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F453" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G453" s="1"/>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A454" s="2">
         <v>45867</v>
       </c>
@@ -8762,9 +10149,12 @@
       <c r="E454" s="1">
         <v>0</v>
       </c>
-      <c r="F454" s="1"/>
-    </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F454" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G454" s="1"/>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A455" s="2">
         <v>45867</v>
       </c>
@@ -8780,9 +10170,12 @@
       <c r="E455" s="1">
         <v>1</v>
       </c>
-      <c r="F455" s="1"/>
-    </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F455" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G455" s="1"/>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A456" s="2">
         <v>45867</v>
       </c>
@@ -8798,9 +10191,12 @@
       <c r="E456" s="1">
         <v>0</v>
       </c>
-      <c r="F456" s="1"/>
-    </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F456" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G456" s="1"/>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A457" s="2">
         <v>45867</v>
       </c>
@@ -8816,9 +10212,12 @@
       <c r="E457" s="1">
         <v>0</v>
       </c>
-      <c r="F457" s="1"/>
-    </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F457" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G457" s="1"/>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A458" s="2">
         <v>45867</v>
       </c>
@@ -8834,9 +10233,12 @@
       <c r="E458" s="1">
         <v>0</v>
       </c>
-      <c r="F458" s="1"/>
-    </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F458" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G458" s="1"/>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A459" s="2">
         <v>45867</v>
       </c>
@@ -8852,9 +10254,12 @@
       <c r="E459" s="1">
         <v>0</v>
       </c>
-      <c r="F459" s="1"/>
-    </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F459" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G459" s="1"/>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A460" s="2">
         <v>45867</v>
       </c>
@@ -8870,9 +10275,12 @@
       <c r="E460" s="1">
         <v>0</v>
       </c>
-      <c r="F460" s="1"/>
-    </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F460" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G460" s="1"/>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A461" s="2">
         <v>45867</v>
       </c>
@@ -8888,9 +10296,12 @@
       <c r="E461" s="1">
         <v>0</v>
       </c>
-      <c r="F461" s="1"/>
-    </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F461" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G461" s="1"/>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A462" s="2">
         <v>45867</v>
       </c>
@@ -8906,9 +10317,12 @@
       <c r="E462" s="1">
         <v>0</v>
       </c>
-      <c r="F462" s="1"/>
-    </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F462" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G462" s="1"/>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A463" s="2">
         <v>45867</v>
       </c>
@@ -8924,9 +10338,12 @@
       <c r="E463" s="1">
         <v>0</v>
       </c>
-      <c r="F463" s="1"/>
-    </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F463" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G463" s="1"/>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A464" s="2">
         <v>45867</v>
       </c>
@@ -8942,9 +10359,12 @@
       <c r="E464" s="1">
         <v>0</v>
       </c>
-      <c r="F464" s="1"/>
-    </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F464" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G464" s="1"/>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A465" s="2">
         <v>45867</v>
       </c>
@@ -8960,9 +10380,12 @@
       <c r="E465" s="1">
         <v>1</v>
       </c>
-      <c r="F465" s="1"/>
-    </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F465" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G465" s="1"/>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A466" s="2">
         <v>45867</v>
       </c>
@@ -8978,9 +10401,12 @@
       <c r="E466" s="1">
         <v>0</v>
       </c>
-      <c r="F466" s="1"/>
-    </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F466" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G466" s="1"/>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A467" s="2">
         <v>45867</v>
       </c>
@@ -8996,9 +10422,12 @@
       <c r="E467" s="1">
         <v>0</v>
       </c>
-      <c r="F467" s="1"/>
-    </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F467" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G467" s="1"/>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A468" s="2">
         <v>45867</v>
       </c>
@@ -9014,9 +10443,12 @@
       <c r="E468" s="1">
         <v>0</v>
       </c>
-      <c r="F468" s="1"/>
-    </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F468" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G468" s="1"/>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A469" s="2">
         <v>45867</v>
       </c>
@@ -9032,9 +10464,12 @@
       <c r="E469" s="1">
         <v>1</v>
       </c>
-      <c r="F469" s="1"/>
-    </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F469" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G469" s="1"/>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A470" s="2">
         <v>45867</v>
       </c>
@@ -9050,9 +10485,12 @@
       <c r="E470" s="1">
         <v>0</v>
       </c>
-      <c r="F470" s="1"/>
-    </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F470" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G470" s="1"/>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A471" s="2">
         <v>45867</v>
       </c>
@@ -9068,9 +10506,12 @@
       <c r="E471" s="1">
         <v>0</v>
       </c>
-      <c r="F471" s="1"/>
-    </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F471" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G471" s="1"/>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A472" s="2">
         <v>45867</v>
       </c>
@@ -9086,9 +10527,12 @@
       <c r="E472" s="1">
         <v>0</v>
       </c>
-      <c r="F472" s="1"/>
-    </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F472" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G472" s="1"/>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A473" s="2">
         <v>45867</v>
       </c>
@@ -9104,9 +10548,12 @@
       <c r="E473" s="1">
         <v>0</v>
       </c>
-      <c r="F473" s="1"/>
-    </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F473" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G473" s="1"/>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A474" s="2">
         <v>45867</v>
       </c>
@@ -9122,9 +10569,12 @@
       <c r="E474" s="1">
         <v>0</v>
       </c>
-      <c r="F474" s="1"/>
-    </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F474" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G474" s="1"/>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A475" s="2">
         <v>45867</v>
       </c>
@@ -9140,9 +10590,12 @@
       <c r="E475" s="1">
         <v>0</v>
       </c>
-      <c r="F475" s="1"/>
-    </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F475" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G475" s="1"/>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A476" s="2">
         <v>45867</v>
       </c>
@@ -9158,9 +10611,12 @@
       <c r="E476" s="1">
         <v>0</v>
       </c>
-      <c r="F476" s="1"/>
-    </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F476" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G476" s="1"/>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A477" s="2">
         <v>45867</v>
       </c>
@@ -9176,9 +10632,12 @@
       <c r="E477" s="1">
         <v>2</v>
       </c>
-      <c r="F477" s="1"/>
-    </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F477" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G477" s="1"/>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A478" s="2">
         <v>45867</v>
       </c>
@@ -9194,9 +10653,12 @@
       <c r="E478" s="1">
         <v>0</v>
       </c>
-      <c r="F478" s="1"/>
-    </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F478" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G478" s="1"/>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A479" s="2">
         <v>45867</v>
       </c>
@@ -9212,9 +10674,12 @@
       <c r="E479" s="1">
         <v>0</v>
       </c>
-      <c r="F479" s="1"/>
-    </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F479" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G479" s="1"/>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A480" s="2">
         <v>45867</v>
       </c>
@@ -9230,9 +10695,12 @@
       <c r="E480" s="1">
         <v>0</v>
       </c>
-      <c r="F480" s="1"/>
-    </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F480" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G480" s="1"/>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A481" s="2">
         <v>45867</v>
       </c>
@@ -9248,9 +10716,12 @@
       <c r="E481" s="1">
         <v>1</v>
       </c>
-      <c r="F481" s="1"/>
-    </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F481" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G481" s="1"/>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A482" s="2">
         <v>45867</v>
       </c>
@@ -9266,9 +10737,12 @@
       <c r="E482" s="1">
         <v>0</v>
       </c>
-      <c r="F482" s="1"/>
-    </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F482" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G482" s="1"/>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A483" s="2">
         <v>45867</v>
       </c>
@@ -9284,9 +10758,12 @@
       <c r="E483" s="1">
         <v>0</v>
       </c>
-      <c r="F483" s="1"/>
-    </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F483" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G483" s="1"/>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A484" s="2">
         <v>45867</v>
       </c>
@@ -9302,9 +10779,12 @@
       <c r="E484" s="1">
         <v>0</v>
       </c>
-      <c r="F484" s="1"/>
-    </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F484" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G484" s="1"/>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A485" s="2">
         <v>45867</v>
       </c>
@@ -9320,9 +10800,12 @@
       <c r="E485" s="1">
         <v>0</v>
       </c>
-      <c r="F485" s="1"/>
-    </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F485" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G485" s="1"/>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A486" s="2">
         <v>45867</v>
       </c>
@@ -9338,9 +10821,12 @@
       <c r="E486" s="1">
         <v>0</v>
       </c>
-      <c r="F486" s="1"/>
-    </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F486" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G486" s="1"/>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A487" s="2">
         <v>45867</v>
       </c>
@@ -9356,9 +10842,12 @@
       <c r="E487" s="1">
         <v>0</v>
       </c>
-      <c r="F487" s="1"/>
-    </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F487" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G487" s="1"/>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A488" s="2">
         <v>45867</v>
       </c>
@@ -9374,9 +10863,12 @@
       <c r="E488" s="1">
         <v>0</v>
       </c>
-      <c r="F488" s="1"/>
-    </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F488" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G488" s="1"/>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A489" s="2">
         <v>45867</v>
       </c>
@@ -9392,9 +10884,12 @@
       <c r="E489" s="1">
         <v>0</v>
       </c>
-      <c r="F489" s="1"/>
-    </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F489" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G489" s="1"/>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A490" s="2">
         <v>45867</v>
       </c>
@@ -9410,9 +10905,12 @@
       <c r="E490" s="1">
         <v>1</v>
       </c>
-      <c r="F490" s="1"/>
-    </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F490" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G490" s="1"/>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A491" s="2">
         <v>45867</v>
       </c>
@@ -9428,9 +10926,12 @@
       <c r="E491" s="1">
         <v>1</v>
       </c>
-      <c r="F491" s="1"/>
-    </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F491" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G491" s="1"/>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A492" s="2">
         <v>45867</v>
       </c>
@@ -9446,9 +10947,12 @@
       <c r="E492" s="1">
         <v>0</v>
       </c>
-      <c r="F492" s="1"/>
-    </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F492" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G492" s="1"/>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A493" s="2">
         <v>45867</v>
       </c>
@@ -9464,9 +10968,12 @@
       <c r="E493" s="1">
         <v>0</v>
       </c>
-      <c r="F493" s="1"/>
-    </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F493" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G493" s="1"/>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A494" s="2">
         <v>45867</v>
       </c>
@@ -9482,9 +10989,12 @@
       <c r="E494" s="1">
         <v>0</v>
       </c>
-      <c r="F494" s="1"/>
-    </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F494" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G494" s="1"/>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A495" s="2">
         <v>45867</v>
       </c>
@@ -9500,9 +11010,12 @@
       <c r="E495" s="1">
         <v>0</v>
       </c>
-      <c r="F495" s="1"/>
-    </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F495" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G495" s="1"/>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A496" s="2">
         <v>45867</v>
       </c>
@@ -9518,9 +11031,12 @@
       <c r="E496" s="1">
         <v>0</v>
       </c>
-      <c r="F496" s="1"/>
-    </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F496" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G496" s="1"/>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A497" s="2">
         <v>45867</v>
       </c>
@@ -9536,9 +11052,12 @@
       <c r="E497" s="1">
         <v>0</v>
       </c>
-      <c r="F497" s="1"/>
-    </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F497" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G497" s="1"/>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A498" s="2">
         <v>45867</v>
       </c>
@@ -9554,9 +11073,12 @@
       <c r="E498" s="1">
         <v>0</v>
       </c>
-      <c r="F498" s="1"/>
-    </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F498" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G498" s="1"/>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A499" s="2">
         <v>45867</v>
       </c>
@@ -9572,9 +11094,12 @@
       <c r="E499" s="1">
         <v>0</v>
       </c>
-      <c r="F499" s="1"/>
-    </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F499" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G499" s="1"/>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A500" s="2">
         <v>45867</v>
       </c>
@@ -9590,9 +11115,12 @@
       <c r="E500" s="1">
         <v>1</v>
       </c>
-      <c r="F500" s="1"/>
-    </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F500" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G500" s="1"/>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A501" s="2">
         <v>45867</v>
       </c>
@@ -9608,7 +11136,10 @@
       <c r="E501" s="1">
         <v>1</v>
       </c>
-      <c r="F501" s="1"/>
+      <c r="F501" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G501" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
